--- a/output/pms/Phát_triển_ứng_dụng_web/PM_IT106.xlsx
+++ b/output/pms/Phát_triển_ứng_dụng_web/PM_IT106.xlsx
@@ -639,7 +639,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J53"/>
+  <dimension ref="A1:J54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1229,7 +1229,7 @@
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>Lesson 01: Câu lệnh Điều kiện if, if-else và if-elif-else</t>
+          <t>Lesson 01: Câu lệnh Điều kiện if và Cấu trúc if-else</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="G16" s="5" t="inlineStr">
         <is>
-          <t>Trình bày và thực hành thành công Câu lệnh Điều kiện if, if-else và if-elif-else.</t>
+          <t>Trình bày và thực hành thành công Câu lệnh Điều kiện if và Cấu trúc if-else.</t>
         </is>
       </c>
       <c r="H16" s="5" t="inlineStr">
@@ -1259,23 +1259,23 @@
       </c>
     </row>
     <row r="17" ht="24" customHeight="1">
-      <c r="A17" s="13" t="n"/>
-      <c r="B17" s="13" t="n"/>
-      <c r="C17" s="13" t="n"/>
-      <c r="D17" s="13" t="n"/>
+      <c r="A17" s="12" t="n"/>
+      <c r="B17" s="12" t="n"/>
+      <c r="C17" s="12" t="n"/>
+      <c r="D17" s="12" t="n"/>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>Lesson 02: Câu lệnh Rẽ nhánh switch-case và Toán tử Ba ngôi Ternary</t>
+          <t>Lesson 02: Câu lệnh Rẽ nhánh Nhiều Trường hợp switch-case</t>
         </is>
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>Cú pháp switch-case với từ khóa break; Toán tử ba ngôi condition ? a : b ngắn gọn.</t>
+          <t>Cú pháp switch-case với từ khóa break; Xử lý nhánh mặc định default.</t>
         </is>
       </c>
       <c r="G17" s="5" t="inlineStr">
         <is>
-          <t>Trình bày và thực hành thành công Câu lệnh Rẽ nhánh switch-case và Toán tử Ba ngôi Ternary.</t>
+          <t>Trình bày và thực hành thành công Câu lệnh Rẽ nhánh Nhiều Trường hợp switch-case.</t>
         </is>
       </c>
       <c r="H17" s="5" t="inlineStr">
@@ -1295,1472 +1295,1456 @@
       </c>
     </row>
     <row r="18" ht="24" customHeight="1">
-      <c r="A18" s="14" t="inlineStr">
+      <c r="A18" s="13" t="n"/>
+      <c r="B18" s="13" t="n"/>
+      <c r="C18" s="13" t="n"/>
+      <c r="D18" s="13" t="n"/>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>Lesson 03: Biểu thức Điều kiện Ba ngôi Ternary Operator</t>
+        </is>
+      </c>
+      <c r="F18" s="5" t="inlineStr">
+        <is>
+          <t>Cú pháp toán tử ba ngôi condition ? a : b ngắn gọn; Ứng dụng gán giá trị điều kiện.</t>
+        </is>
+      </c>
+      <c r="G18" s="5" t="inlineStr">
+        <is>
+          <t>Trình bày và thực hành thành công Biểu thức Điều kiện Ba ngôi Ternary Operator.</t>
+        </is>
+      </c>
+      <c r="H18" s="5" t="inlineStr">
+        <is>
+          <t>CẤM: Các khái niệm nâng cao chưa học ở các bài tiếp theo.</t>
+        </is>
+      </c>
+      <c r="I18" s="5" t="inlineStr">
+        <is>
+          <t>ĐÃ HỌC: Các kiến thức JS đã học ở các bài trước.</t>
+        </is>
+      </c>
+      <c r="J18" s="5" t="inlineStr">
+        <is>
+          <t>JavaScript Vanilla (ES6+), HTML5/CSS3, DOM API, Fetch API, Async/Await, Cursor AI IDE</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="24" customHeight="1">
+      <c r="A19" s="14" t="inlineStr">
         <is>
           <t>Session 07</t>
         </is>
       </c>
-      <c r="B18" s="14" t="inlineStr">
+      <c r="B19" s="14" t="inlineStr">
         <is>
           <t>Thực hành</t>
         </is>
       </c>
-      <c r="C18" s="14" t="inlineStr">
+      <c r="C19" s="14" t="inlineStr">
         <is>
           <t>PRACTICE</t>
         </is>
       </c>
-      <c r="D18" s="15" t="inlineStr">
+      <c r="D19" s="15" t="inlineStr">
         <is>
           <t>Session 07 - Thực hành Lập trình Logic Kiểm tra Ràng buộc và Phân loại Người dùng</t>
         </is>
       </c>
-      <c r="E18" s="16" t="inlineStr">
+      <c r="E19" s="16" t="inlineStr">
         <is>
           <t>Session 07 - Thực hành Lập trình Logic Kiểm tra Ràng buộc và Phân loại Người dùng</t>
         </is>
       </c>
-      <c r="F18" s="16" t="inlineStr">
+      <c r="F19" s="16" t="inlineStr">
         <is>
           <t>Thực hành Lập trình Logic Kiểm tra Ràng buộc và Phân loại Người dùng</t>
         </is>
       </c>
-      <c r="G18" s="16" t="inlineStr">
+      <c r="G19" s="16" t="inlineStr">
         <is>
           <t>Hoàn thành các mục tiêu học tập và năng lực thực hành của Thực hành Lập trình Logic Kiểm tra Ràng buộc và Phân loại Người dùng.</t>
         </is>
       </c>
-      <c r="H18" s="16" t="inlineStr">
+      <c r="H19" s="16" t="inlineStr">
         <is>
           <t>CẤM: Các chủ đề nâng cao chưa học ở các buổi tiếp theo.</t>
         </is>
       </c>
-      <c r="I18" s="16" t="inlineStr">
+      <c r="I19" s="16" t="inlineStr">
         <is>
           <t>ĐÃ HỌC: Các kiến thức tiền đề đã tích lũy từ các buổi trước.</t>
         </is>
       </c>
-      <c r="J18" s="16" t="inlineStr">
-        <is>
-          <t>JavaScript Vanilla (ES6+), HTML5/CSS3, DOM API, Fetch API, Async/Await, Cursor AI IDE</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="24" customHeight="1">
-      <c r="A19" s="10" t="inlineStr">
+      <c r="J19" s="16" t="inlineStr">
+        <is>
+          <t>JavaScript Vanilla (ES6+), HTML5/CSS3, DOM API, Fetch API, Async/Await, Cursor AI IDE</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="24" customHeight="1">
+      <c r="A20" s="10" t="inlineStr">
         <is>
           <t>Session 08</t>
         </is>
       </c>
-      <c r="B19" s="10" t="inlineStr">
+      <c r="B20" s="10" t="inlineStr">
         <is>
           <t>Lý thuyết</t>
         </is>
       </c>
-      <c r="C19" s="10" t="inlineStr">
+      <c r="C20" s="10" t="inlineStr">
         <is>
           <t>THEORY</t>
         </is>
       </c>
-      <c r="D19" s="11" t="inlineStr">
+      <c r="D20" s="11" t="inlineStr">
         <is>
           <t>Session 08 - Cấu trúc Vòng lặp for, while, do-while và Điều khiển Luồng</t>
         </is>
       </c>
-      <c r="E19" s="5" t="inlineStr">
+      <c r="E20" s="5" t="inlineStr">
         <is>
           <t>Lesson 01: Vòng lặp for cơ bản và Vòng lặp while</t>
         </is>
       </c>
-      <c r="F19" s="5" t="inlineStr">
+      <c r="F20" s="5" t="inlineStr">
         <is>
           <t>Cú pháp for (let i=0; i&lt;n; i++); Vòng lặp điều kiện while; Vòng lặp do-while.</t>
         </is>
       </c>
-      <c r="G19" s="5" t="inlineStr">
+      <c r="G20" s="5" t="inlineStr">
         <is>
           <t>Trình bày và thực hành thành công Vòng lặp for cơ bản và Vòng lặp while.</t>
         </is>
       </c>
-      <c r="H19" s="5" t="inlineStr">
-        <is>
-          <t>CẤM: Các khái niệm nâng cao chưa học ở các bài tiếp theo.</t>
-        </is>
-      </c>
-      <c r="I19" s="5" t="inlineStr">
-        <is>
-          <t>ĐÃ HỌC: Các kiến thức JS đã học ở các bài trước.</t>
-        </is>
-      </c>
-      <c r="J19" s="5" t="inlineStr">
-        <is>
-          <t>JavaScript Vanilla (ES6+), HTML5/CSS3, DOM API, Fetch API, Async/Await, Cursor AI IDE</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="24" customHeight="1">
-      <c r="A20" s="13" t="n"/>
-      <c r="B20" s="13" t="n"/>
-      <c r="C20" s="13" t="n"/>
-      <c r="D20" s="13" t="n"/>
-      <c r="E20" s="5" t="inlineStr">
+      <c r="H20" s="5" t="inlineStr">
+        <is>
+          <t>CẤM: Các khái niệm nâng cao chưa học ở các bài tiếp theo.</t>
+        </is>
+      </c>
+      <c r="I20" s="5" t="inlineStr">
+        <is>
+          <t>ĐÃ HỌC: Các kiến thức JS đã học ở các bài trước.</t>
+        </is>
+      </c>
+      <c r="J20" s="5" t="inlineStr">
+        <is>
+          <t>JavaScript Vanilla (ES6+), HTML5/CSS3, DOM API, Fetch API, Async/Await, Cursor AI IDE</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="24" customHeight="1">
+      <c r="A21" s="13" t="n"/>
+      <c r="B21" s="13" t="n"/>
+      <c r="C21" s="13" t="n"/>
+      <c r="D21" s="13" t="n"/>
+      <c r="E21" s="5" t="inlineStr">
         <is>
           <t>Lesson 02: Điều khiển Luồng lặp với break, continue</t>
         </is>
       </c>
-      <c r="F20" s="5" t="inlineStr">
+      <c r="F21" s="5" t="inlineStr">
         <is>
           <t>Sử dụng break ngắt lặp và continue bỏ qua lượt lặp khi thỏa điều kiện.</t>
         </is>
       </c>
-      <c r="G20" s="5" t="inlineStr">
+      <c r="G21" s="5" t="inlineStr">
         <is>
           <t>Trình bày và thực hành thành công Điều khiển Luồng lặp với break, continue.</t>
         </is>
       </c>
-      <c r="H20" s="5" t="inlineStr">
-        <is>
-          <t>CẤM: Các khái niệm nâng cao chưa học ở các bài tiếp theo.</t>
-        </is>
-      </c>
-      <c r="I20" s="5" t="inlineStr">
-        <is>
-          <t>ĐÃ HỌC: Các kiến thức JS đã học ở các bài trước.</t>
-        </is>
-      </c>
-      <c r="J20" s="5" t="inlineStr">
-        <is>
-          <t>JavaScript Vanilla (ES6+), HTML5/CSS3, DOM API, Fetch API, Async/Await, Cursor AI IDE</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="24" customHeight="1">
-      <c r="A21" s="14" t="inlineStr">
+      <c r="H21" s="5" t="inlineStr">
+        <is>
+          <t>CẤM: Các khái niệm nâng cao chưa học ở các bài tiếp theo.</t>
+        </is>
+      </c>
+      <c r="I21" s="5" t="inlineStr">
+        <is>
+          <t>ĐÃ HỌC: Các kiến thức JS đã học ở các bài trước.</t>
+        </is>
+      </c>
+      <c r="J21" s="5" t="inlineStr">
+        <is>
+          <t>JavaScript Vanilla (ES6+), HTML5/CSS3, DOM API, Fetch API, Async/Await, Cursor AI IDE</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="24" customHeight="1">
+      <c r="A22" s="14" t="inlineStr">
         <is>
           <t>Session 09</t>
         </is>
       </c>
-      <c r="B21" s="14" t="inlineStr">
+      <c r="B22" s="14" t="inlineStr">
         <is>
           <t>Thực hành</t>
         </is>
       </c>
-      <c r="C21" s="14" t="inlineStr">
+      <c r="C22" s="14" t="inlineStr">
         <is>
           <t>PRACTICE</t>
         </is>
       </c>
-      <c r="D21" s="15" t="inlineStr">
+      <c r="D22" s="15" t="inlineStr">
         <is>
           <t>Session 09 - Thực hành Duyệt Chuỗi và Tính toán Thuật toán Lặp Dữ liệu Console</t>
         </is>
       </c>
-      <c r="E21" s="16" t="inlineStr">
+      <c r="E22" s="16" t="inlineStr">
         <is>
           <t>Session 09 - Thực hành Duyệt Chuỗi và Tính toán Thuật toán Lặp Dữ liệu Console</t>
         </is>
       </c>
-      <c r="F21" s="16" t="inlineStr">
+      <c r="F22" s="16" t="inlineStr">
         <is>
           <t>Thực hành Duyệt Chuỗi và Tính toán Thuật toán Lặp Dữ liệu Console</t>
         </is>
       </c>
-      <c r="G21" s="16" t="inlineStr">
+      <c r="G22" s="16" t="inlineStr">
         <is>
           <t>Hoàn thành các mục tiêu học tập và năng lực thực hành của Thực hành Duyệt Chuỗi và Tính toán Thuật toán Lặp Dữ liệu Console.</t>
         </is>
       </c>
-      <c r="H21" s="16" t="inlineStr">
+      <c r="H22" s="16" t="inlineStr">
         <is>
           <t>CẤM: Các chủ đề nâng cao chưa học ở các buổi tiếp theo.</t>
         </is>
       </c>
-      <c r="I21" s="16" t="inlineStr">
+      <c r="I22" s="16" t="inlineStr">
         <is>
           <t>ĐÃ HỌC: Các kiến thức tiền đề đã tích lũy từ các buổi trước.</t>
         </is>
       </c>
-      <c r="J21" s="16" t="inlineStr">
-        <is>
-          <t>JavaScript Vanilla (ES6+), HTML5/CSS3, DOM API, Fetch API, Async/Await, Cursor AI IDE</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="24" customHeight="1">
-      <c r="A22" s="10" t="inlineStr">
+      <c r="J22" s="16" t="inlineStr">
+        <is>
+          <t>JavaScript Vanilla (ES6+), HTML5/CSS3, DOM API, Fetch API, Async/Await, Cursor AI IDE</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="24" customHeight="1">
+      <c r="A23" s="10" t="inlineStr">
         <is>
           <t>Session 10</t>
         </is>
       </c>
-      <c r="B22" s="10" t="inlineStr">
+      <c r="B23" s="10" t="inlineStr">
         <is>
           <t>Lý thuyết</t>
         </is>
       </c>
-      <c r="C22" s="10" t="inlineStr">
+      <c r="C23" s="10" t="inlineStr">
         <is>
           <t>THEORY</t>
         </is>
       </c>
-      <c r="D22" s="11" t="inlineStr">
+      <c r="D23" s="11" t="inlineStr">
         <is>
           <t>Session 10 - Mảng Dữ liệu (Array) trong JavaScript và các Thao tác CRUD Cơ bản</t>
         </is>
       </c>
-      <c r="E22" s="5" t="inlineStr">
+      <c r="E23" s="5" t="inlineStr">
         <is>
           <t>Lesson 01: Khái niệm Array, Indexing và Độ dài .length</t>
         </is>
       </c>
-      <c r="F22" s="5" t="inlineStr">
+      <c r="F23" s="5" t="inlineStr">
         <is>
           <t>Khai báo mảng []; Chỉ số phần tử 0-indexed; Truy cập phần tử và thuộc tính .length.</t>
         </is>
       </c>
-      <c r="G22" s="5" t="inlineStr">
+      <c r="G23" s="5" t="inlineStr">
         <is>
           <t>Trình bày và thực hành thành công Khái niệm Array, Indexing và Độ dài .length.</t>
         </is>
       </c>
-      <c r="H22" s="5" t="inlineStr">
-        <is>
-          <t>CẤM: Các khái niệm nâng cao chưa học ở các bài tiếp theo.</t>
-        </is>
-      </c>
-      <c r="I22" s="5" t="inlineStr">
-        <is>
-          <t>ĐÃ HỌC: Các kiến thức JS đã học ở các bài trước.</t>
-        </is>
-      </c>
-      <c r="J22" s="5" t="inlineStr">
-        <is>
-          <t>JavaScript Vanilla (ES6+), HTML5/CSS3, DOM API, Fetch API, Async/Await, Cursor AI IDE</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="24" customHeight="1">
-      <c r="A23" s="12" t="n"/>
-      <c r="B23" s="12" t="n"/>
-      <c r="C23" s="12" t="n"/>
-      <c r="D23" s="12" t="n"/>
-      <c r="E23" s="5" t="inlineStr">
+      <c r="H23" s="5" t="inlineStr">
+        <is>
+          <t>CẤM: Các khái niệm nâng cao chưa học ở các bài tiếp theo.</t>
+        </is>
+      </c>
+      <c r="I23" s="5" t="inlineStr">
+        <is>
+          <t>ĐÃ HỌC: Các kiến thức JS đã học ở các bài trước.</t>
+        </is>
+      </c>
+      <c r="J23" s="5" t="inlineStr">
+        <is>
+          <t>JavaScript Vanilla (ES6+), HTML5/CSS3, DOM API, Fetch API, Async/Await, Cursor AI IDE</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="24" customHeight="1">
+      <c r="A24" s="12" t="n"/>
+      <c r="B24" s="12" t="n"/>
+      <c r="C24" s="12" t="n"/>
+      <c r="D24" s="12" t="n"/>
+      <c r="E24" s="5" t="inlineStr">
         <is>
           <t>Lesson 02: Duyệt Mảng và Thao tác Thêm phần tử (push, unshift)</t>
         </is>
       </c>
-      <c r="F23" s="5" t="inlineStr">
+      <c r="F24" s="5" t="inlineStr">
         <is>
           <t>Duyệt mảng bằng vòng lặp for và for...of; Thêm phần tử mới với .push() và .unshift().</t>
         </is>
       </c>
-      <c r="G23" s="5" t="inlineStr">
+      <c r="G24" s="5" t="inlineStr">
         <is>
           <t>Trình bày và thực hành thành công Duyệt Mảng và Thao tác Thêm phần tử (push, unshift).</t>
         </is>
       </c>
-      <c r="H23" s="5" t="inlineStr">
-        <is>
-          <t>CẤM: Các khái niệm nâng cao chưa học ở các bài tiếp theo.</t>
-        </is>
-      </c>
-      <c r="I23" s="5" t="inlineStr">
-        <is>
-          <t>ĐÃ HỌC: Các kiến thức JS đã học ở các bài trước.</t>
-        </is>
-      </c>
-      <c r="J23" s="5" t="inlineStr">
-        <is>
-          <t>JavaScript Vanilla (ES6+), HTML5/CSS3, DOM API, Fetch API, Async/Await, Cursor AI IDE</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="24" customHeight="1">
-      <c r="A24" s="13" t="n"/>
-      <c r="B24" s="13" t="n"/>
-      <c r="C24" s="13" t="n"/>
-      <c r="D24" s="13" t="n"/>
-      <c r="E24" s="5" t="inlineStr">
+      <c r="H24" s="5" t="inlineStr">
+        <is>
+          <t>CẤM: Các khái niệm nâng cao chưa học ở các bài tiếp theo.</t>
+        </is>
+      </c>
+      <c r="I24" s="5" t="inlineStr">
+        <is>
+          <t>ĐÃ HỌC: Các kiến thức JS đã học ở các bài trước.</t>
+        </is>
+      </c>
+      <c r="J24" s="5" t="inlineStr">
+        <is>
+          <t>JavaScript Vanilla (ES6+), HTML5/CSS3, DOM API, Fetch API, Async/Await, Cursor AI IDE</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="24" customHeight="1">
+      <c r="A25" s="13" t="n"/>
+      <c r="B25" s="13" t="n"/>
+      <c r="C25" s="13" t="n"/>
+      <c r="D25" s="13" t="n"/>
+      <c r="E25" s="5" t="inlineStr">
         <is>
           <t>Lesson 03: Thao tác Sửa và Xóa phần tử Mảng (pop, shift, splice)</t>
         </is>
       </c>
-      <c r="F24" s="5" t="inlineStr">
+      <c r="F25" s="5" t="inlineStr">
         <is>
           <t>Cập nhật giá trị theo chỉ số; Xóa phần tử với .pop(), .shift(), .splice().</t>
         </is>
       </c>
-      <c r="G24" s="5" t="inlineStr">
+      <c r="G25" s="5" t="inlineStr">
         <is>
           <t>Trình bày và thực hành thành công Thao tác Sửa và Xóa phần tử Mảng (pop, shift, splice).</t>
         </is>
       </c>
-      <c r="H24" s="5" t="inlineStr">
-        <is>
-          <t>CẤM: Các khái niệm nâng cao chưa học ở các bài tiếp theo.</t>
-        </is>
-      </c>
-      <c r="I24" s="5" t="inlineStr">
-        <is>
-          <t>ĐÃ HỌC: Các kiến thức JS đã học ở các bài trước.</t>
-        </is>
-      </c>
-      <c r="J24" s="5" t="inlineStr">
-        <is>
-          <t>JavaScript Vanilla (ES6+), HTML5/CSS3, DOM API, Fetch API, Async/Await, Cursor AI IDE</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="24" customHeight="1">
-      <c r="A25" s="14" t="inlineStr">
+      <c r="H25" s="5" t="inlineStr">
+        <is>
+          <t>CẤM: Các khái niệm nâng cao chưa học ở các bài tiếp theo.</t>
+        </is>
+      </c>
+      <c r="I25" s="5" t="inlineStr">
+        <is>
+          <t>ĐÃ HỌC: Các kiến thức JS đã học ở các bài trước.</t>
+        </is>
+      </c>
+      <c r="J25" s="5" t="inlineStr">
+        <is>
+          <t>JavaScript Vanilla (ES6+), HTML5/CSS3, DOM API, Fetch API, Async/Await, Cursor AI IDE</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="24" customHeight="1">
+      <c r="A26" s="14" t="inlineStr">
         <is>
           <t>Session 11</t>
         </is>
       </c>
-      <c r="B25" s="14" t="inlineStr">
+      <c r="B26" s="14" t="inlineStr">
         <is>
           <t>Thực hành</t>
         </is>
       </c>
-      <c r="C25" s="14" t="inlineStr">
+      <c r="C26" s="14" t="inlineStr">
         <is>
           <t>PRACTICE</t>
         </is>
       </c>
-      <c r="D25" s="15" t="inlineStr">
+      <c r="D26" s="15" t="inlineStr">
         <is>
           <t>Session 11 - Thực hành Quản lý Danh sách Sản phẩm bằng Mảng JavaScript</t>
         </is>
       </c>
-      <c r="E25" s="16" t="inlineStr">
+      <c r="E26" s="16" t="inlineStr">
         <is>
           <t>Session 11 - Thực hành Quản lý Danh sách Sản phẩm bằng Mảng JavaScript</t>
         </is>
       </c>
-      <c r="F25" s="16" t="inlineStr">
+      <c r="F26" s="16" t="inlineStr">
         <is>
           <t>Thực hành Quản lý Danh sách Sản phẩm bằng Mảng JavaScript</t>
         </is>
       </c>
-      <c r="G25" s="16" t="inlineStr">
+      <c r="G26" s="16" t="inlineStr">
         <is>
           <t>Hoàn thành các mục tiêu học tập và năng lực thực hành của Thực hành Quản lý Danh sách Sản phẩm bằng Mảng JavaScript.</t>
         </is>
       </c>
-      <c r="H25" s="16" t="inlineStr">
+      <c r="H26" s="16" t="inlineStr">
         <is>
           <t>CẤM: Các chủ đề nâng cao chưa học ở các buổi tiếp theo.</t>
         </is>
       </c>
-      <c r="I25" s="16" t="inlineStr">
+      <c r="I26" s="16" t="inlineStr">
         <is>
           <t>ĐÃ HỌC: Các kiến thức tiền đề đã tích lũy từ các buổi trước.</t>
         </is>
       </c>
-      <c r="J25" s="16" t="inlineStr">
-        <is>
-          <t>JavaScript Vanilla (ES6+), HTML5/CSS3, DOM API, Fetch API, Async/Await, Cursor AI IDE</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="24" customHeight="1">
-      <c r="A26" s="10" t="inlineStr">
+      <c r="J26" s="16" t="inlineStr">
+        <is>
+          <t>JavaScript Vanilla (ES6+), HTML5/CSS3, DOM API, Fetch API, Async/Await, Cursor AI IDE</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="24" customHeight="1">
+      <c r="A27" s="10" t="inlineStr">
         <is>
           <t>Session 12</t>
         </is>
       </c>
-      <c r="B26" s="10" t="inlineStr">
+      <c r="B27" s="10" t="inlineStr">
         <is>
           <t>Lý thuyết</t>
         </is>
       </c>
-      <c r="C26" s="10" t="inlineStr">
+      <c r="C27" s="10" t="inlineStr">
         <is>
           <t>THEORY</t>
         </is>
       </c>
-      <c r="D26" s="11" t="inlineStr">
+      <c r="D27" s="11" t="inlineStr">
         <is>
           <t>Session 12 - Đối tượng (Object) trong JavaScript, Cấu trúc JSON và Thao tác CRUD</t>
         </is>
       </c>
-      <c r="E26" s="5" t="inlineStr">
+      <c r="E27" s="5" t="inlineStr">
         <is>
           <t>Lesson 01: Khái niệm Object Literal (Key-Value)</t>
         </is>
       </c>
-      <c r="F26" s="5" t="inlineStr">
+      <c r="F27" s="5" t="inlineStr">
         <is>
           <t>Khai báo đối tượng {}; Khóa và giá trị; Truy cập thuộc tính qua dot notation (.) và bracket notation ([]).</t>
         </is>
       </c>
-      <c r="G26" s="5" t="inlineStr">
+      <c r="G27" s="5" t="inlineStr">
         <is>
           <t>Trình bày và thực hành thành công Khái niệm Object Literal (Key-Value).</t>
         </is>
       </c>
-      <c r="H26" s="5" t="inlineStr">
-        <is>
-          <t>CẤM: Các khái niệm nâng cao chưa học ở các bài tiếp theo.</t>
-        </is>
-      </c>
-      <c r="I26" s="5" t="inlineStr">
-        <is>
-          <t>ĐÃ HỌC: Các kiến thức JS đã học ở các bài trước.</t>
-        </is>
-      </c>
-      <c r="J26" s="5" t="inlineStr">
-        <is>
-          <t>JavaScript Vanilla (ES6+), HTML5/CSS3, DOM API, Fetch API, Async/Await, Cursor AI IDE</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="24" customHeight="1">
-      <c r="A27" s="13" t="n"/>
-      <c r="B27" s="13" t="n"/>
-      <c r="C27" s="13" t="n"/>
-      <c r="D27" s="13" t="n"/>
-      <c r="E27" s="5" t="inlineStr">
+      <c r="H27" s="5" t="inlineStr">
+        <is>
+          <t>CẤM: Các khái niệm nâng cao chưa học ở các bài tiếp theo.</t>
+        </is>
+      </c>
+      <c r="I27" s="5" t="inlineStr">
+        <is>
+          <t>ĐÃ HỌC: Các kiến thức JS đã học ở các bài trước.</t>
+        </is>
+      </c>
+      <c r="J27" s="5" t="inlineStr">
+        <is>
+          <t>JavaScript Vanilla (ES6+), HTML5/CSS3, DOM API, Fetch API, Async/Await, Cursor AI IDE</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="24" customHeight="1">
+      <c r="A28" s="13" t="n"/>
+      <c r="B28" s="13" t="n"/>
+      <c r="C28" s="13" t="n"/>
+      <c r="D28" s="13" t="n"/>
+      <c r="E28" s="5" t="inlineStr">
         <is>
           <t>Lesson 02: Thao tác Thêm, Sửa, Xóa Thuộc tính Object và Cấu trúc JSON</t>
         </is>
       </c>
-      <c r="F27" s="5" t="inlineStr">
+      <c r="F28" s="5" t="inlineStr">
         <is>
           <t>Thêm/sửa thuộc tính; Xóa thuộc tính với từ khóa delete; Chuyển đổi JSON.stringify() và JSON.parse().</t>
         </is>
       </c>
-      <c r="G27" s="5" t="inlineStr">
+      <c r="G28" s="5" t="inlineStr">
         <is>
           <t>Trình bày và thực hành thành công Thao tác Thêm, Sửa, Xóa Thuộc tính Object và Cấu trúc JSON.</t>
         </is>
       </c>
-      <c r="H27" s="5" t="inlineStr">
-        <is>
-          <t>CẤM: Các khái niệm nâng cao chưa học ở các bài tiếp theo.</t>
-        </is>
-      </c>
-      <c r="I27" s="5" t="inlineStr">
-        <is>
-          <t>ĐÃ HỌC: Các kiến thức JS đã học ở các bài trước.</t>
-        </is>
-      </c>
-      <c r="J27" s="5" t="inlineStr">
-        <is>
-          <t>JavaScript Vanilla (ES6+), HTML5/CSS3, DOM API, Fetch API, Async/Await, Cursor AI IDE</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="24" customHeight="1">
-      <c r="A28" s="17" t="inlineStr">
+      <c r="H28" s="5" t="inlineStr">
+        <is>
+          <t>CẤM: Các khái niệm nâng cao chưa học ở các bài tiếp theo.</t>
+        </is>
+      </c>
+      <c r="I28" s="5" t="inlineStr">
+        <is>
+          <t>ĐÃ HỌC: Các kiến thức JS đã học ở các bài trước.</t>
+        </is>
+      </c>
+      <c r="J28" s="5" t="inlineStr">
+        <is>
+          <t>JavaScript Vanilla (ES6+), HTML5/CSS3, DOM API, Fetch API, Async/Await, Cursor AI IDE</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="24" customHeight="1">
+      <c r="A29" s="17" t="inlineStr">
         <is>
           <t>Session 13</t>
         </is>
       </c>
-      <c r="B28" s="17" t="inlineStr">
+      <c r="B29" s="17" t="inlineStr">
         <is>
           <t>Mini project</t>
         </is>
       </c>
-      <c r="C28" s="17" t="inlineStr">
+      <c r="C29" s="17" t="inlineStr">
         <is>
           <t>MINI_PROJECT</t>
         </is>
       </c>
-      <c r="D28" s="18" t="inlineStr">
+      <c r="D29" s="18" t="inlineStr">
         <is>
           <t>Session 13 - Mini Project 1: Xây dựng Ứng dụng Quản lý Danh mục Bán hàng Console (Phần 1)</t>
         </is>
       </c>
-      <c r="E28" s="19" t="inlineStr">
+      <c r="E29" s="19" t="inlineStr">
         <is>
           <t>Session 13 - Mini Project 1: Xây dựng Ứng dụng Quản lý Danh mục Bán hàng Console (Phần 1)</t>
         </is>
       </c>
-      <c r="F28" s="19" t="inlineStr">
+      <c r="F29" s="19" t="inlineStr">
         <is>
           <t>Mini Project 1: Xây dựng Ứng dụng Quản lý Danh mục Bán hàng Console (Phần 1)</t>
         </is>
       </c>
-      <c r="G28" s="19" t="inlineStr">
+      <c r="G29" s="19" t="inlineStr">
         <is>
           <t>Hoàn thành các mục tiêu học tập và năng lực thực hành của Mini Project 1: Xây dựng Ứng dụng Quản lý Danh mục Bán hàng Console (Phần 1).</t>
         </is>
       </c>
-      <c r="H28" s="19" t="inlineStr">
+      <c r="H29" s="19" t="inlineStr">
         <is>
           <t>CẤM: Các chủ đề nâng cao chưa học ở các buổi tiếp theo.</t>
         </is>
       </c>
-      <c r="I28" s="19" t="inlineStr">
+      <c r="I29" s="19" t="inlineStr">
         <is>
           <t>ĐÃ HỌC: Các kiến thức tiền đề đã tích lũy từ các buổi trước.</t>
         </is>
       </c>
-      <c r="J28" s="19" t="inlineStr">
-        <is>
-          <t>JavaScript Vanilla (ES6+), HTML5/CSS3, DOM API, Fetch API, Async/Await, Cursor AI IDE</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="24" customHeight="1">
-      <c r="A29" s="10" t="inlineStr">
+      <c r="J29" s="19" t="inlineStr">
+        <is>
+          <t>JavaScript Vanilla (ES6+), HTML5/CSS3, DOM API, Fetch API, Async/Await, Cursor AI IDE</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="24" customHeight="1">
+      <c r="A30" s="10" t="inlineStr">
         <is>
           <t>Session 14</t>
         </is>
       </c>
-      <c r="B29" s="10" t="inlineStr">
+      <c r="B30" s="10" t="inlineStr">
         <is>
           <t>Lý thuyết</t>
         </is>
       </c>
-      <c r="C29" s="10" t="inlineStr">
+      <c r="C30" s="10" t="inlineStr">
         <is>
           <t>THEORY</t>
         </is>
       </c>
-      <c r="D29" s="11" t="inlineStr">
+      <c r="D30" s="11" t="inlineStr">
         <is>
           <t>Session 14 - Tổ chức Hàm (Function), Tham số, Arrow Function và Phạm vi Scope</t>
         </is>
       </c>
-      <c r="E29" s="5" t="inlineStr">
+      <c r="E30" s="5" t="inlineStr">
         <is>
           <t>Lesson 01: Khai báo Hàm (Function Declaration &amp; Expression)</t>
         </is>
       </c>
-      <c r="F29" s="5" t="inlineStr">
+      <c r="F30" s="5" t="inlineStr">
         <is>
           <t>Khai báo hàm với từ khóa function; Truyền tham số và lệnh return trả về giá trị.</t>
         </is>
       </c>
-      <c r="G29" s="5" t="inlineStr">
+      <c r="G30" s="5" t="inlineStr">
         <is>
           <t>Trình bày và thực hành thành công Khai báo Hàm (Function Declaration &amp; Expression).</t>
         </is>
       </c>
-      <c r="H29" s="5" t="inlineStr">
-        <is>
-          <t>CẤM: Các khái niệm nâng cao chưa học ở các bài tiếp theo.</t>
-        </is>
-      </c>
-      <c r="I29" s="5" t="inlineStr">
-        <is>
-          <t>ĐÃ HỌC: Các kiến thức JS đã học ở các bài trước.</t>
-        </is>
-      </c>
-      <c r="J29" s="5" t="inlineStr">
-        <is>
-          <t>JavaScript Vanilla (ES6+), HTML5/CSS3, DOM API, Fetch API, Async/Await, Cursor AI IDE</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="24" customHeight="1">
-      <c r="A30" s="12" t="n"/>
-      <c r="B30" s="12" t="n"/>
-      <c r="C30" s="12" t="n"/>
-      <c r="D30" s="12" t="n"/>
-      <c r="E30" s="5" t="inlineStr">
+      <c r="H30" s="5" t="inlineStr">
+        <is>
+          <t>CẤM: Các khái niệm nâng cao chưa học ở các bài tiếp theo.</t>
+        </is>
+      </c>
+      <c r="I30" s="5" t="inlineStr">
+        <is>
+          <t>ĐÃ HỌC: Các kiến thức JS đã học ở các bài trước.</t>
+        </is>
+      </c>
+      <c r="J30" s="5" t="inlineStr">
+        <is>
+          <t>JavaScript Vanilla (ES6+), HTML5/CSS3, DOM API, Fetch API, Async/Await, Cursor AI IDE</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="24" customHeight="1">
+      <c r="A31" s="12" t="n"/>
+      <c r="B31" s="12" t="n"/>
+      <c r="C31" s="12" t="n"/>
+      <c r="D31" s="12" t="n"/>
+      <c r="E31" s="5" t="inlineStr">
         <is>
           <t>Lesson 02: Cú pháp Arrow Function ES6 và Tham số Mặc định</t>
         </is>
       </c>
-      <c r="F30" s="5" t="inlineStr">
+      <c r="F31" s="5" t="inlineStr">
         <is>
           <t>Cú pháp ngắn gọn Arrow Function () =&gt; {}; Thiết lập default parameters.</t>
         </is>
       </c>
-      <c r="G30" s="5" t="inlineStr">
+      <c r="G31" s="5" t="inlineStr">
         <is>
           <t>Trình bày và thực hành thành công Cú pháp Arrow Function ES6 và Tham số Mặc định.</t>
         </is>
       </c>
-      <c r="H30" s="5" t="inlineStr">
-        <is>
-          <t>CẤM: Các khái niệm nâng cao chưa học ở các bài tiếp theo.</t>
-        </is>
-      </c>
-      <c r="I30" s="5" t="inlineStr">
-        <is>
-          <t>ĐÃ HỌC: Các kiến thức JS đã học ở các bài trước.</t>
-        </is>
-      </c>
-      <c r="J30" s="5" t="inlineStr">
-        <is>
-          <t>JavaScript Vanilla (ES6+), HTML5/CSS3, DOM API, Fetch API, Async/Await, Cursor AI IDE</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="24" customHeight="1">
-      <c r="A31" s="13" t="n"/>
-      <c r="B31" s="13" t="n"/>
-      <c r="C31" s="13" t="n"/>
-      <c r="D31" s="13" t="n"/>
-      <c r="E31" s="5" t="inlineStr">
+      <c r="H31" s="5" t="inlineStr">
+        <is>
+          <t>CẤM: Các khái niệm nâng cao chưa học ở các bài tiếp theo.</t>
+        </is>
+      </c>
+      <c r="I31" s="5" t="inlineStr">
+        <is>
+          <t>ĐÃ HỌC: Các kiến thức JS đã học ở các bài trước.</t>
+        </is>
+      </c>
+      <c r="J31" s="5" t="inlineStr">
+        <is>
+          <t>JavaScript Vanilla (ES6+), HTML5/CSS3, DOM API, Fetch API, Async/Await, Cursor AI IDE</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="24" customHeight="1">
+      <c r="A32" s="13" t="n"/>
+      <c r="B32" s="13" t="n"/>
+      <c r="C32" s="13" t="n"/>
+      <c r="D32" s="13" t="n"/>
+      <c r="E32" s="5" t="inlineStr">
         <is>
           <t>Lesson 03: Phạm vi Biến Global, Local Scope và Closures cơ bản</t>
         </is>
       </c>
-      <c r="F31" s="5" t="inlineStr">
+      <c r="F32" s="5" t="inlineStr">
         <is>
           <t>Phân biệt phạm vi toàn cục và cục bộ; Khái niệm Hoisting và Closures trong JS.</t>
         </is>
       </c>
-      <c r="G31" s="5" t="inlineStr">
+      <c r="G32" s="5" t="inlineStr">
         <is>
           <t>Trình bày và thực hành thành công Phạm vi Biến Global, Local Scope và Closures cơ bản.</t>
         </is>
       </c>
-      <c r="H31" s="5" t="inlineStr">
-        <is>
-          <t>CẤM: Các khái niệm nâng cao chưa học ở các bài tiếp theo.</t>
-        </is>
-      </c>
-      <c r="I31" s="5" t="inlineStr">
-        <is>
-          <t>ĐÃ HỌC: Các kiến thức JS đã học ở các bài trước.</t>
-        </is>
-      </c>
-      <c r="J31" s="5" t="inlineStr">
-        <is>
-          <t>JavaScript Vanilla (ES6+), HTML5/CSS3, DOM API, Fetch API, Async/Await, Cursor AI IDE</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="24" customHeight="1">
-      <c r="A32" s="10" t="inlineStr">
+      <c r="H32" s="5" t="inlineStr">
+        <is>
+          <t>CẤM: Các khái niệm nâng cao chưa học ở các bài tiếp theo.</t>
+        </is>
+      </c>
+      <c r="I32" s="5" t="inlineStr">
+        <is>
+          <t>ĐÃ HỌC: Các kiến thức JS đã học ở các bài trước.</t>
+        </is>
+      </c>
+      <c r="J32" s="5" t="inlineStr">
+        <is>
+          <t>JavaScript Vanilla (ES6+), HTML5/CSS3, DOM API, Fetch API, Async/Await, Cursor AI IDE</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="24" customHeight="1">
+      <c r="A33" s="10" t="inlineStr">
         <is>
           <t>Session 15</t>
         </is>
       </c>
-      <c r="B32" s="10" t="inlineStr">
+      <c r="B33" s="10" t="inlineStr">
         <is>
           <t>Lý thuyết</t>
         </is>
       </c>
-      <c r="C32" s="10" t="inlineStr">
+      <c r="C33" s="10" t="inlineStr">
         <is>
           <t>THEORY</t>
         </is>
       </c>
-      <c r="D32" s="11" t="inlineStr">
+      <c r="D33" s="11" t="inlineStr">
         <is>
           <t>Session 15 - Ôn tập Tổng hợp Kiến thức JavaScript Cú pháp, Mảng, Object và Hàm</t>
         </is>
       </c>
-      <c r="E32" s="5" t="inlineStr">
+      <c r="E33" s="5" t="inlineStr">
         <is>
           <t>Lesson 01: Hệ thống hóa Cấu trúc Dữ liệu và Hàm trong JS</t>
         </is>
       </c>
-      <c r="F32" s="5" t="inlineStr">
+      <c r="F33" s="5" t="inlineStr">
         <is>
           <t>Ôn tập mảng, object, hàm; Quy chuẩn viết mã sạch Clean Code ES6+.</t>
         </is>
       </c>
-      <c r="G32" s="5" t="inlineStr">
+      <c r="G33" s="5" t="inlineStr">
         <is>
           <t>Trình bày và thực hành thành công Hệ thống hóa Cấu trúc Dữ liệu và Hàm trong JS.</t>
         </is>
       </c>
-      <c r="H32" s="5" t="inlineStr">
-        <is>
-          <t>CẤM: Các khái niệm nâng cao chưa học ở các bài tiếp theo.</t>
-        </is>
-      </c>
-      <c r="I32" s="5" t="inlineStr">
-        <is>
-          <t>ĐÃ HỌC: Các kiến thức JS đã học ở các bài trước.</t>
-        </is>
-      </c>
-      <c r="J32" s="5" t="inlineStr">
-        <is>
-          <t>JavaScript Vanilla (ES6+), HTML5/CSS3, DOM API, Fetch API, Async/Await, Cursor AI IDE</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="24" customHeight="1">
-      <c r="A33" s="13" t="n"/>
-      <c r="B33" s="13" t="n"/>
-      <c r="C33" s="13" t="n"/>
-      <c r="D33" s="13" t="n"/>
-      <c r="E33" s="5" t="inlineStr">
+      <c r="H33" s="5" t="inlineStr">
+        <is>
+          <t>CẤM: Các khái niệm nâng cao chưa học ở các bài tiếp theo.</t>
+        </is>
+      </c>
+      <c r="I33" s="5" t="inlineStr">
+        <is>
+          <t>ĐÃ HỌC: Các kiến thức JS đã học ở các bài trước.</t>
+        </is>
+      </c>
+      <c r="J33" s="5" t="inlineStr">
+        <is>
+          <t>JavaScript Vanilla (ES6+), HTML5/CSS3, DOM API, Fetch API, Async/Await, Cursor AI IDE</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="24" customHeight="1">
+      <c r="A34" s="13" t="n"/>
+      <c r="B34" s="13" t="n"/>
+      <c r="C34" s="13" t="n"/>
+      <c r="D34" s="13" t="n"/>
+      <c r="E34" s="5" t="inlineStr">
         <is>
           <t>Lesson 02: Tổ chức Mã nguồn Mô-đun Clean Code JavaScript</t>
         </is>
       </c>
-      <c r="F33" s="5" t="inlineStr">
+      <c r="F34" s="5" t="inlineStr">
         <is>
           <t>Phân rã hàm nhỏ đơn nhiệm và quy chuẩn đặt tên camelCase.</t>
         </is>
       </c>
-      <c r="G33" s="5" t="inlineStr">
+      <c r="G34" s="5" t="inlineStr">
         <is>
           <t>Trình bày và thực hành thành công Tổ chức Mã nguồn Mô-đun Clean Code JavaScript.</t>
         </is>
       </c>
-      <c r="H33" s="5" t="inlineStr">
-        <is>
-          <t>CẤM: Các khái niệm nâng cao chưa học ở các bài tiếp theo.</t>
-        </is>
-      </c>
-      <c r="I33" s="5" t="inlineStr">
-        <is>
-          <t>ĐÃ HỌC: Các kiến thức JS đã học ở các bài trước.</t>
-        </is>
-      </c>
-      <c r="J33" s="5" t="inlineStr">
-        <is>
-          <t>JavaScript Vanilla (ES6+), HTML5/CSS3, DOM API, Fetch API, Async/Await, Cursor AI IDE</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="24" customHeight="1">
-      <c r="A34" s="20" t="inlineStr">
+      <c r="H34" s="5" t="inlineStr">
+        <is>
+          <t>CẤM: Các khái niệm nâng cao chưa học ở các bài tiếp theo.</t>
+        </is>
+      </c>
+      <c r="I34" s="5" t="inlineStr">
+        <is>
+          <t>ĐÃ HỌC: Các kiến thức JS đã học ở các bài trước.</t>
+        </is>
+      </c>
+      <c r="J34" s="5" t="inlineStr">
+        <is>
+          <t>JavaScript Vanilla (ES6+), HTML5/CSS3, DOM API, Fetch API, Async/Await, Cursor AI IDE</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="24" customHeight="1">
+      <c r="A35" s="20" t="inlineStr">
         <is>
           <t>Session 16</t>
         </is>
       </c>
-      <c r="B34" s="20" t="inlineStr">
+      <c r="B35" s="20" t="inlineStr">
         <is>
           <t>Thi giữa môn</t>
         </is>
       </c>
-      <c r="C34" s="20" t="inlineStr">
+      <c r="C35" s="20" t="inlineStr">
         <is>
           <t>MIDTERM</t>
         </is>
       </c>
-      <c r="D34" s="21" t="inlineStr">
+      <c r="D35" s="21" t="inlineStr">
         <is>
           <t>Session 16 - Thi Thực hành Giữa môn: Lập trình Logic Xử lý Dữ liệu JavaScript</t>
         </is>
       </c>
-      <c r="E34" s="22" t="inlineStr">
+      <c r="E35" s="22" t="inlineStr">
         <is>
           <t>Session 16 - Thi Thực hành Giữa môn: Lập trình Logic Xử lý Dữ liệu JavaScript</t>
         </is>
       </c>
-      <c r="F34" s="22" t="inlineStr">
+      <c r="F35" s="22" t="inlineStr">
         <is>
           <t>Thi Thực hành Giữa môn: Lập trình Logic Xử lý Dữ liệu JavaScript</t>
         </is>
       </c>
-      <c r="G34" s="22" t="inlineStr">
+      <c r="G35" s="22" t="inlineStr">
         <is>
           <t>Hoàn thành các mục tiêu học tập và năng lực thực hành của Thi Thực hành Giữa môn: Lập trình Logic Xử lý Dữ liệu JavaScript.</t>
         </is>
       </c>
-      <c r="H34" s="22" t="inlineStr">
+      <c r="H35" s="22" t="inlineStr">
         <is>
           <t>CẤM: Các chủ đề nâng cao chưa học ở các buổi tiếp theo.</t>
         </is>
       </c>
-      <c r="I34" s="22" t="inlineStr">
+      <c r="I35" s="22" t="inlineStr">
         <is>
           <t>ĐÃ HỌC: Các kiến thức tiền đề đã tích lũy từ các buổi trước.</t>
         </is>
       </c>
-      <c r="J34" s="22" t="inlineStr">
-        <is>
-          <t>JavaScript Vanilla (ES6+), HTML5/CSS3, DOM API, Fetch API, Async/Await, Cursor AI IDE</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="24" customHeight="1">
-      <c r="A35" s="10" t="inlineStr">
+      <c r="J35" s="22" t="inlineStr">
+        <is>
+          <t>JavaScript Vanilla (ES6+), HTML5/CSS3, DOM API, Fetch API, Async/Await, Cursor AI IDE</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="24" customHeight="1">
+      <c r="A36" s="10" t="inlineStr">
         <is>
           <t>Session 17</t>
         </is>
       </c>
-      <c r="B35" s="10" t="inlineStr">
+      <c r="B36" s="10" t="inlineStr">
         <is>
           <t>Lý thuyết</t>
         </is>
       </c>
-      <c r="C35" s="10" t="inlineStr">
+      <c r="C36" s="10" t="inlineStr">
         <is>
           <t>THEORY</t>
         </is>
       </c>
-      <c r="D35" s="11" t="inlineStr">
+      <c r="D36" s="11" t="inlineStr">
         <is>
           <t>Session 17 - Tương tác DOM API (Document Object Model): Truy xuất và Thay đổi Nội dung</t>
         </is>
       </c>
-      <c r="E35" s="5" t="inlineStr">
+      <c r="E36" s="5" t="inlineStr">
         <is>
           <t>Lesson 01: Khái niệm DOM Tree và Truy xuất Element</t>
         </is>
       </c>
-      <c r="F35" s="5" t="inlineStr">
+      <c r="F36" s="5" t="inlineStr">
         <is>
           <t>Cấu trúc cây DOM; Truy xuất phần tử bằng getElementById, querySelector, querySelectorAll.</t>
         </is>
       </c>
-      <c r="G35" s="5" t="inlineStr">
+      <c r="G36" s="5" t="inlineStr">
         <is>
           <t>Trình bày và thực hành thành công Khái niệm DOM Tree và Truy xuất Element.</t>
         </is>
       </c>
-      <c r="H35" s="5" t="inlineStr">
-        <is>
-          <t>CẤM: Các khái niệm nâng cao chưa học ở các bài tiếp theo.</t>
-        </is>
-      </c>
-      <c r="I35" s="5" t="inlineStr">
-        <is>
-          <t>ĐÃ HỌC: Các kiến thức JS đã học ở các bài trước.</t>
-        </is>
-      </c>
-      <c r="J35" s="5" t="inlineStr">
-        <is>
-          <t>JavaScript Vanilla (ES6+), HTML5/CSS3, DOM API, Fetch API, Async/Await, Cursor AI IDE</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="24" customHeight="1">
-      <c r="A36" s="13" t="n"/>
-      <c r="B36" s="13" t="n"/>
-      <c r="C36" s="13" t="n"/>
-      <c r="D36" s="13" t="n"/>
-      <c r="E36" s="5" t="inlineStr">
+      <c r="H36" s="5" t="inlineStr">
+        <is>
+          <t>CẤM: Các khái niệm nâng cao chưa học ở các bài tiếp theo.</t>
+        </is>
+      </c>
+      <c r="I36" s="5" t="inlineStr">
+        <is>
+          <t>ĐÃ HỌC: Các kiến thức JS đã học ở các bài trước.</t>
+        </is>
+      </c>
+      <c r="J36" s="5" t="inlineStr">
+        <is>
+          <t>JavaScript Vanilla (ES6+), HTML5/CSS3, DOM API, Fetch API, Async/Await, Cursor AI IDE</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="24" customHeight="1">
+      <c r="A37" s="13" t="n"/>
+      <c r="B37" s="13" t="n"/>
+      <c r="C37" s="13" t="n"/>
+      <c r="D37" s="13" t="n"/>
+      <c r="E37" s="5" t="inlineStr">
         <is>
           <t>Lesson 02: Thay đổi Nội dung HTML và Thuộc tính Element</t>
         </is>
       </c>
-      <c r="F36" s="5" t="inlineStr">
+      <c r="F37" s="5" t="inlineStr">
         <is>
           <t>Thay đổi textContent, innerHTML, src, href; Thao tác với classList (add, remove, toggle).</t>
         </is>
       </c>
-      <c r="G36" s="5" t="inlineStr">
+      <c r="G37" s="5" t="inlineStr">
         <is>
           <t>Trình bày và thực hành thành công Thay đổi Nội dung HTML và Thuộc tính Element.</t>
         </is>
       </c>
-      <c r="H36" s="5" t="inlineStr">
-        <is>
-          <t>CẤM: Các khái niệm nâng cao chưa học ở các bài tiếp theo.</t>
-        </is>
-      </c>
-      <c r="I36" s="5" t="inlineStr">
-        <is>
-          <t>ĐÃ HỌC: Các kiến thức JS đã học ở các bài trước.</t>
-        </is>
-      </c>
-      <c r="J36" s="5" t="inlineStr">
-        <is>
-          <t>JavaScript Vanilla (ES6+), HTML5/CSS3, DOM API, Fetch API, Async/Await, Cursor AI IDE</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="24" customHeight="1">
-      <c r="A37" s="14" t="inlineStr">
+      <c r="H37" s="5" t="inlineStr">
+        <is>
+          <t>CẤM: Các khái niệm nâng cao chưa học ở các bài tiếp theo.</t>
+        </is>
+      </c>
+      <c r="I37" s="5" t="inlineStr">
+        <is>
+          <t>ĐÃ HỌC: Các kiến thức JS đã học ở các bài trước.</t>
+        </is>
+      </c>
+      <c r="J37" s="5" t="inlineStr">
+        <is>
+          <t>JavaScript Vanilla (ES6+), HTML5/CSS3, DOM API, Fetch API, Async/Await, Cursor AI IDE</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="24" customHeight="1">
+      <c r="A38" s="14" t="inlineStr">
         <is>
           <t>Session 18</t>
         </is>
       </c>
-      <c r="B37" s="14" t="inlineStr">
+      <c r="B38" s="14" t="inlineStr">
         <is>
           <t>Thực hành</t>
         </is>
       </c>
-      <c r="C37" s="14" t="inlineStr">
+      <c r="C38" s="14" t="inlineStr">
         <is>
           <t>PRACTICE</t>
         </is>
       </c>
-      <c r="D37" s="15" t="inlineStr">
+      <c r="D38" s="15" t="inlineStr">
         <is>
           <t>Session 18 - Thực hành Truy xuất DOM và Cập nhật Giao diện Web Động</t>
         </is>
       </c>
-      <c r="E37" s="16" t="inlineStr">
+      <c r="E38" s="16" t="inlineStr">
         <is>
           <t>Session 18 - Thực hành Truy xuất DOM và Cập nhật Giao diện Web Động</t>
         </is>
       </c>
-      <c r="F37" s="16" t="inlineStr">
+      <c r="F38" s="16" t="inlineStr">
         <is>
           <t>Thực hành Truy xuất DOM và Cập nhật Giao diện Web Động</t>
         </is>
       </c>
-      <c r="G37" s="16" t="inlineStr">
+      <c r="G38" s="16" t="inlineStr">
         <is>
           <t>Hoàn thành các mục tiêu học tập và năng lực thực hành của Thực hành Truy xuất DOM và Cập nhật Giao diện Web Động.</t>
         </is>
       </c>
-      <c r="H37" s="16" t="inlineStr">
+      <c r="H38" s="16" t="inlineStr">
         <is>
           <t>CẤM: Các chủ đề nâng cao chưa học ở các buổi tiếp theo.</t>
         </is>
       </c>
-      <c r="I37" s="16" t="inlineStr">
+      <c r="I38" s="16" t="inlineStr">
         <is>
           <t>ĐÃ HỌC: Các kiến thức tiền đề đã tích lũy từ các buổi trước.</t>
         </is>
       </c>
-      <c r="J37" s="16" t="inlineStr">
-        <is>
-          <t>JavaScript Vanilla (ES6+), HTML5/CSS3, DOM API, Fetch API, Async/Await, Cursor AI IDE</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="24" customHeight="1">
-      <c r="A38" s="10" t="inlineStr">
+      <c r="J38" s="16" t="inlineStr">
+        <is>
+          <t>JavaScript Vanilla (ES6+), HTML5/CSS3, DOM API, Fetch API, Async/Await, Cursor AI IDE</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="24" customHeight="1">
+      <c r="A39" s="10" t="inlineStr">
         <is>
           <t>Session 19</t>
         </is>
       </c>
-      <c r="B38" s="10" t="inlineStr">
+      <c r="B39" s="10" t="inlineStr">
         <is>
           <t>Lý thuyết</t>
         </is>
       </c>
-      <c r="C38" s="10" t="inlineStr">
+      <c r="C39" s="10" t="inlineStr">
         <is>
           <t>THEORY</t>
         </is>
       </c>
-      <c r="D38" s="11" t="inlineStr">
+      <c r="D39" s="11" t="inlineStr">
         <is>
           <t>Session 19 - Xử lý Sự kiện Người dùng (Event Handling) và Sự kiện Form Input</t>
         </is>
       </c>
-      <c r="E38" s="5" t="inlineStr">
+      <c r="E39" s="5" t="inlineStr">
         <is>
           <t>Lesson 01: Đăng ký Sự kiện với addEventListener</t>
         </is>
       </c>
-      <c r="F38" s="5" t="inlineStr">
+      <c r="F39" s="5" t="inlineStr">
         <is>
           <t>Các sự kiện click, dblclick, mouseover; Đăng ký xử lý sự kiện qua addEventListener.</t>
         </is>
       </c>
-      <c r="G38" s="5" t="inlineStr">
+      <c r="G39" s="5" t="inlineStr">
         <is>
           <t>Trình bày và thực hành thành công Đăng ký Sự kiện với addEventListener.</t>
         </is>
       </c>
-      <c r="H38" s="5" t="inlineStr">
-        <is>
-          <t>CẤM: Các khái niệm nâng cao chưa học ở các bài tiếp theo.</t>
-        </is>
-      </c>
-      <c r="I38" s="5" t="inlineStr">
-        <is>
-          <t>ĐÃ HỌC: Các kiến thức JS đã học ở các bài trước.</t>
-        </is>
-      </c>
-      <c r="J38" s="5" t="inlineStr">
-        <is>
-          <t>JavaScript Vanilla (ES6+), HTML5/CSS3, DOM API, Fetch API, Async/Await, Cursor AI IDE</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="24" customHeight="1">
-      <c r="A39" s="13" t="n"/>
-      <c r="B39" s="13" t="n"/>
-      <c r="C39" s="13" t="n"/>
-      <c r="D39" s="13" t="n"/>
-      <c r="E39" s="5" t="inlineStr">
+      <c r="H39" s="5" t="inlineStr">
+        <is>
+          <t>CẤM: Các khái niệm nâng cao chưa học ở các bài tiếp theo.</t>
+        </is>
+      </c>
+      <c r="I39" s="5" t="inlineStr">
+        <is>
+          <t>ĐÃ HỌC: Các kiến thức JS đã học ở các bài trước.</t>
+        </is>
+      </c>
+      <c r="J39" s="5" t="inlineStr">
+        <is>
+          <t>JavaScript Vanilla (ES6+), HTML5/CSS3, DOM API, Fetch API, Async/Await, Cursor AI IDE</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="24" customHeight="1">
+      <c r="A40" s="13" t="n"/>
+      <c r="B40" s="13" t="n"/>
+      <c r="C40" s="13" t="n"/>
+      <c r="D40" s="13" t="n"/>
+      <c r="E40" s="5" t="inlineStr">
         <is>
           <t>Lesson 02: Làm việc với Form, Input và Sự kiện submit</t>
         </is>
       </c>
-      <c r="F39" s="5" t="inlineStr">
+      <c r="F40" s="5" t="inlineStr">
         <is>
           <t>Lấy giá trị từ input field; Ngăn chặn load trang mặc định với event.preventDefault(); Validation form.</t>
         </is>
       </c>
-      <c r="G39" s="5" t="inlineStr">
+      <c r="G40" s="5" t="inlineStr">
         <is>
           <t>Trình bày và thực hành thành công Làm việc với Form, Input và Sự kiện submit.</t>
         </is>
       </c>
-      <c r="H39" s="5" t="inlineStr">
-        <is>
-          <t>CẤM: Các khái niệm nâng cao chưa học ở các bài tiếp theo.</t>
-        </is>
-      </c>
-      <c r="I39" s="5" t="inlineStr">
-        <is>
-          <t>ĐÃ HỌC: Các kiến thức JS đã học ở các bài trước.</t>
-        </is>
-      </c>
-      <c r="J39" s="5" t="inlineStr">
-        <is>
-          <t>JavaScript Vanilla (ES6+), HTML5/CSS3, DOM API, Fetch API, Async/Await, Cursor AI IDE</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="24" customHeight="1">
-      <c r="A40" s="14" t="inlineStr">
+      <c r="H40" s="5" t="inlineStr">
+        <is>
+          <t>CẤM: Các khái niệm nâng cao chưa học ở các bài tiếp theo.</t>
+        </is>
+      </c>
+      <c r="I40" s="5" t="inlineStr">
+        <is>
+          <t>ĐÃ HỌC: Các kiến thức JS đã học ở các bài trước.</t>
+        </is>
+      </c>
+      <c r="J40" s="5" t="inlineStr">
+        <is>
+          <t>JavaScript Vanilla (ES6+), HTML5/CSS3, DOM API, Fetch API, Async/Await, Cursor AI IDE</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="24" customHeight="1">
+      <c r="A41" s="14" t="inlineStr">
         <is>
           <t>Session 20</t>
         </is>
       </c>
-      <c r="B40" s="14" t="inlineStr">
+      <c r="B41" s="14" t="inlineStr">
         <is>
           <t>Thực hành</t>
         </is>
       </c>
-      <c r="C40" s="14" t="inlineStr">
+      <c r="C41" s="14" t="inlineStr">
         <is>
           <t>PRACTICE</t>
         </is>
       </c>
-      <c r="D40" s="15" t="inlineStr">
+      <c r="D41" s="15" t="inlineStr">
         <is>
           <t>Session 20 - Thực hành Xây dựng Form Đăng nhập và Đăng ký Tương tác Tối ưu UI</t>
         </is>
       </c>
-      <c r="E40" s="16" t="inlineStr">
+      <c r="E41" s="16" t="inlineStr">
         <is>
           <t>Session 20 - Thực hành Xây dựng Form Đăng nhập và Đăng ký Tương tác Tối ưu UI</t>
         </is>
       </c>
-      <c r="F40" s="16" t="inlineStr">
+      <c r="F41" s="16" t="inlineStr">
         <is>
           <t>Thực hành Xây dựng Form Đăng nhập và Đăng ký Tương tác Tối ưu UI</t>
         </is>
       </c>
-      <c r="G40" s="16" t="inlineStr">
+      <c r="G41" s="16" t="inlineStr">
         <is>
           <t>Hoàn thành các mục tiêu học tập và năng lực thực hành của Thực hành Xây dựng Form Đăng nhập và Đăng ký Tương tác Tối ưu UI.</t>
         </is>
       </c>
-      <c r="H40" s="16" t="inlineStr">
+      <c r="H41" s="16" t="inlineStr">
         <is>
           <t>CẤM: Các chủ đề nâng cao chưa học ở các buổi tiếp theo.</t>
         </is>
       </c>
-      <c r="I40" s="16" t="inlineStr">
+      <c r="I41" s="16" t="inlineStr">
         <is>
           <t>ĐÃ HỌC: Các kiến thức tiền đề đã tích lũy từ các buổi trước.</t>
         </is>
       </c>
-      <c r="J40" s="16" t="inlineStr">
-        <is>
-          <t>JavaScript Vanilla (ES6+), HTML5/CSS3, DOM API, Fetch API, Async/Await, Cursor AI IDE</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="24" customHeight="1">
-      <c r="A41" s="10" t="inlineStr">
+      <c r="J41" s="16" t="inlineStr">
+        <is>
+          <t>JavaScript Vanilla (ES6+), HTML5/CSS3, DOM API, Fetch API, Async/Await, Cursor AI IDE</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="24" customHeight="1">
+      <c r="A42" s="10" t="inlineStr">
         <is>
           <t>Session 21</t>
         </is>
       </c>
-      <c r="B41" s="10" t="inlineStr">
+      <c r="B42" s="10" t="inlineStr">
         <is>
           <t>Lý thuyết</t>
         </is>
       </c>
-      <c r="C41" s="10" t="inlineStr">
+      <c r="C42" s="10" t="inlineStr">
         <is>
           <t>THEORY</t>
         </is>
       </c>
-      <c r="D41" s="11" t="inlineStr">
+      <c r="D42" s="11" t="inlineStr">
         <is>
           <t>Session 21 - Lập trình Bất đồng bộ: Callback, Promise và Async/Await với Fetch API</t>
         </is>
       </c>
-      <c r="E41" s="5" t="inlineStr">
+      <c r="E42" s="5" t="inlineStr">
         <is>
           <t>Lesson 01: Khái niệm Lập trình Bất đồng bộ và Promise</t>
         </is>
       </c>
-      <c r="F41" s="5" t="inlineStr">
+      <c r="F42" s="5" t="inlineStr">
         <is>
           <t>So sánh đồng bộ và bất đồng bộ; Khái niệm Promise (Pending, Fulfilled, Rejected).</t>
         </is>
       </c>
-      <c r="G41" s="5" t="inlineStr">
+      <c r="G42" s="5" t="inlineStr">
         <is>
           <t>Trình bày và thực hành thành công Khái niệm Lập trình Bất đồng bộ và Promise.</t>
         </is>
       </c>
-      <c r="H41" s="5" t="inlineStr">
-        <is>
-          <t>CẤM: Các khái niệm nâng cao chưa học ở các bài tiếp theo.</t>
-        </is>
-      </c>
-      <c r="I41" s="5" t="inlineStr">
-        <is>
-          <t>ĐÃ HỌC: Các kiến thức JS đã học ở các bài trước.</t>
-        </is>
-      </c>
-      <c r="J41" s="5" t="inlineStr">
-        <is>
-          <t>JavaScript Vanilla (ES6+), HTML5/CSS3, DOM API, Fetch API, Async/Await, Cursor AI IDE</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="24" customHeight="1">
-      <c r="A42" s="13" t="n"/>
-      <c r="B42" s="13" t="n"/>
-      <c r="C42" s="13" t="n"/>
-      <c r="D42" s="13" t="n"/>
-      <c r="E42" s="5" t="inlineStr">
+      <c r="H42" s="5" t="inlineStr">
+        <is>
+          <t>CẤM: Các khái niệm nâng cao chưa học ở các bài tiếp theo.</t>
+        </is>
+      </c>
+      <c r="I42" s="5" t="inlineStr">
+        <is>
+          <t>ĐÃ HỌC: Các kiến thức JS đã học ở các bài trước.</t>
+        </is>
+      </c>
+      <c r="J42" s="5" t="inlineStr">
+        <is>
+          <t>JavaScript Vanilla (ES6+), HTML5/CSS3, DOM API, Fetch API, Async/Await, Cursor AI IDE</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="24" customHeight="1">
+      <c r="A43" s="13" t="n"/>
+      <c r="B43" s="13" t="n"/>
+      <c r="C43" s="13" t="n"/>
+      <c r="D43" s="13" t="n"/>
+      <c r="E43" s="5" t="inlineStr">
         <is>
           <t>Lesson 02: Cú pháp Async/Await và Gọi API với Fetch</t>
         </is>
       </c>
-      <c r="F42" s="5" t="inlineStr">
+      <c r="F43" s="5" t="inlineStr">
         <is>
           <t>Sử dụng async/await xử lý bất đồng bộ; Gọi API lấy dữ liệu JSON bằng fetch().</t>
         </is>
       </c>
-      <c r="G42" s="5" t="inlineStr">
+      <c r="G43" s="5" t="inlineStr">
         <is>
           <t>Trình bày và thực hành thành công Cú pháp Async/Await và Gọi API với Fetch.</t>
         </is>
       </c>
-      <c r="H42" s="5" t="inlineStr">
-        <is>
-          <t>CẤM: Các khái niệm nâng cao chưa học ở các bài tiếp theo.</t>
-        </is>
-      </c>
-      <c r="I42" s="5" t="inlineStr">
-        <is>
-          <t>ĐÃ HỌC: Các kiến thức JS đã học ở các bài trước.</t>
-        </is>
-      </c>
-      <c r="J42" s="5" t="inlineStr">
-        <is>
-          <t>JavaScript Vanilla (ES6+), HTML5/CSS3, DOM API, Fetch API, Async/Await, Cursor AI IDE</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="24" customHeight="1">
-      <c r="A43" s="17" t="inlineStr">
+      <c r="H43" s="5" t="inlineStr">
+        <is>
+          <t>CẤM: Các khái niệm nâng cao chưa học ở các bài tiếp theo.</t>
+        </is>
+      </c>
+      <c r="I43" s="5" t="inlineStr">
+        <is>
+          <t>ĐÃ HỌC: Các kiến thức JS đã học ở các bài trước.</t>
+        </is>
+      </c>
+      <c r="J43" s="5" t="inlineStr">
+        <is>
+          <t>JavaScript Vanilla (ES6+), HTML5/CSS3, DOM API, Fetch API, Async/Await, Cursor AI IDE</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="24" customHeight="1">
+      <c r="A44" s="17" t="inlineStr">
         <is>
           <t>Session 22</t>
         </is>
       </c>
-      <c r="B43" s="17" t="inlineStr">
+      <c r="B44" s="17" t="inlineStr">
         <is>
           <t>Mini project</t>
         </is>
       </c>
-      <c r="C43" s="17" t="inlineStr">
+      <c r="C44" s="17" t="inlineStr">
         <is>
           <t>MINI_PROJECT</t>
         </is>
       </c>
-      <c r="D43" s="18" t="inlineStr">
+      <c r="D44" s="18" t="inlineStr">
         <is>
           <t>Session 22 - Mini Project 2: Xây dựng Dashboard Web Tương tác Gọi Fetch API Dữ liệu Động</t>
         </is>
       </c>
-      <c r="E43" s="19" t="inlineStr">
+      <c r="E44" s="19" t="inlineStr">
         <is>
           <t>Session 22 - Mini Project 2: Xây dựng Dashboard Web Tương tác Gọi Fetch API Dữ liệu Động</t>
         </is>
       </c>
-      <c r="F43" s="19" t="inlineStr">
+      <c r="F44" s="19" t="inlineStr">
         <is>
           <t>Mini Project 2: Xây dựng Dashboard Web Tương tác Gọi Fetch API Dữ liệu Động</t>
         </is>
       </c>
-      <c r="G43" s="19" t="inlineStr">
+      <c r="G44" s="19" t="inlineStr">
         <is>
           <t>Hoàn thành các mục tiêu học tập và năng lực thực hành của Mini Project 2: Xây dựng Dashboard Web Tương tác Gọi Fetch API Dữ liệu Động.</t>
         </is>
       </c>
-      <c r="H43" s="19" t="inlineStr">
+      <c r="H44" s="19" t="inlineStr">
         <is>
           <t>CẤM: Các chủ đề nâng cao chưa học ở các buổi tiếp theo.</t>
         </is>
       </c>
-      <c r="I43" s="19" t="inlineStr">
+      <c r="I44" s="19" t="inlineStr">
         <is>
           <t>ĐÃ HỌC: Các kiến thức tiền đề đã tích lũy từ các buổi trước.</t>
         </is>
       </c>
-      <c r="J43" s="19" t="inlineStr">
-        <is>
-          <t>JavaScript Vanilla (ES6+), HTML5/CSS3, DOM API, Fetch API, Async/Await, Cursor AI IDE</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="24" customHeight="1">
-      <c r="A44" s="10" t="inlineStr">
+      <c r="J44" s="19" t="inlineStr">
+        <is>
+          <t>JavaScript Vanilla (ES6+), HTML5/CSS3, DOM API, Fetch API, Async/Await, Cursor AI IDE</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="24" customHeight="1">
+      <c r="A45" s="10" t="inlineStr">
         <is>
           <t>Session 23</t>
         </is>
       </c>
-      <c r="B44" s="10" t="inlineStr">
+      <c r="B45" s="10" t="inlineStr">
         <is>
           <t>Lý thuyết</t>
         </is>
       </c>
-      <c r="C44" s="10" t="inlineStr">
+      <c r="C45" s="10" t="inlineStr">
         <is>
           <t>THEORY</t>
         </is>
       </c>
-      <c r="D44" s="11" t="inlineStr">
+      <c r="D45" s="11" t="inlineStr">
         <is>
           <t>Session 23 - Lưu trữ Dữ liệu Trình duyệt với LocalStorage và SessionStorage</t>
         </is>
       </c>
-      <c r="E44" s="5" t="inlineStr">
+      <c r="E45" s="5" t="inlineStr">
         <is>
           <t>Lesson 01: Lưu trữ LocalStorage và SessionStorage</t>
         </is>
       </c>
-      <c r="F44" s="5" t="inlineStr">
+      <c r="F45" s="5" t="inlineStr">
         <is>
           <t>Cơ chế lưu trữ Client-side; Thao tác setItem(), getItem(), removeItem(), clear(); Lưu object với JSON.</t>
         </is>
       </c>
-      <c r="G44" s="5" t="inlineStr">
+      <c r="G45" s="5" t="inlineStr">
         <is>
           <t>Trình bày và thực hành thành công Lưu trữ LocalStorage và SessionStorage.</t>
         </is>
       </c>
-      <c r="H44" s="5" t="inlineStr">
-        <is>
-          <t>CẤM: Các khái niệm nâng cao chưa học ở các bài tiếp theo.</t>
-        </is>
-      </c>
-      <c r="I44" s="5" t="inlineStr">
-        <is>
-          <t>ĐÃ HỌC: Các kiến thức JS đã học ở các bài trước.</t>
-        </is>
-      </c>
-      <c r="J44" s="5" t="inlineStr">
-        <is>
-          <t>JavaScript Vanilla (ES6+), HTML5/CSS3, DOM API, Fetch API, Async/Await, Cursor AI IDE</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" ht="24" customHeight="1">
-      <c r="A45" s="13" t="n"/>
-      <c r="B45" s="13" t="n"/>
-      <c r="C45" s="13" t="n"/>
-      <c r="D45" s="13" t="n"/>
-      <c r="E45" s="5" t="inlineStr">
+      <c r="H45" s="5" t="inlineStr">
+        <is>
+          <t>CẤM: Các khái niệm nâng cao chưa học ở các bài tiếp theo.</t>
+        </is>
+      </c>
+      <c r="I45" s="5" t="inlineStr">
+        <is>
+          <t>ĐÃ HỌC: Các kiến thức JS đã học ở các bài trước.</t>
+        </is>
+      </c>
+      <c r="J45" s="5" t="inlineStr">
+        <is>
+          <t>JavaScript Vanilla (ES6+), HTML5/CSS3, DOM API, Fetch API, Async/Await, Cursor AI IDE</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="24" customHeight="1">
+      <c r="A46" s="13" t="n"/>
+      <c r="B46" s="13" t="n"/>
+      <c r="C46" s="13" t="n"/>
+      <c r="D46" s="13" t="n"/>
+      <c r="E46" s="5" t="inlineStr">
         <is>
           <t>Lesson 02: Tích hợp LocalStorage Bảo tồn Trạng thái Web</t>
         </is>
       </c>
-      <c r="F45" s="5" t="inlineStr">
+      <c r="F46" s="5" t="inlineStr">
         <is>
           <t>Ứng dụng LocalStorage lưu danh sách giỏ hàng, chế độ Dark/Light mode.</t>
         </is>
       </c>
-      <c r="G45" s="5" t="inlineStr">
+      <c r="G46" s="5" t="inlineStr">
         <is>
           <t>Trình bày và thực hành thành công Tích hợp LocalStorage Bảo tồn Trạng thái Web.</t>
         </is>
       </c>
-      <c r="H45" s="5" t="inlineStr">
-        <is>
-          <t>CẤM: Các khái niệm nâng cao chưa học ở các bài tiếp theo.</t>
-        </is>
-      </c>
-      <c r="I45" s="5" t="inlineStr">
-        <is>
-          <t>ĐÃ HỌC: Các kiến thức JS đã học ở các bài trước.</t>
-        </is>
-      </c>
-      <c r="J45" s="5" t="inlineStr">
-        <is>
-          <t>JavaScript Vanilla (ES6+), HTML5/CSS3, DOM API, Fetch API, Async/Await, Cursor AI IDE</t>
-        </is>
-      </c>
-    </row>
-    <row r="46" ht="24" customHeight="1">
-      <c r="A46" s="14" t="inlineStr">
+      <c r="H46" s="5" t="inlineStr">
+        <is>
+          <t>CẤM: Các khái niệm nâng cao chưa học ở các bài tiếp theo.</t>
+        </is>
+      </c>
+      <c r="I46" s="5" t="inlineStr">
+        <is>
+          <t>ĐÃ HỌC: Các kiến thức JS đã học ở các bài trước.</t>
+        </is>
+      </c>
+      <c r="J46" s="5" t="inlineStr">
+        <is>
+          <t>JavaScript Vanilla (ES6+), HTML5/CSS3, DOM API, Fetch API, Async/Await, Cursor AI IDE</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="24" customHeight="1">
+      <c r="A47" s="14" t="inlineStr">
         <is>
           <t>Session 24</t>
         </is>
       </c>
-      <c r="B46" s="14" t="inlineStr">
+      <c r="B47" s="14" t="inlineStr">
         <is>
           <t>Thực hành</t>
         </is>
       </c>
-      <c r="C46" s="14" t="inlineStr">
+      <c r="C47" s="14" t="inlineStr">
         <is>
           <t>PRACTICE</t>
         </is>
       </c>
-      <c r="D46" s="15" t="inlineStr">
+      <c r="D47" s="15" t="inlineStr">
         <is>
           <t>Session 24 - Thực hành Xây dựng Ứng dụng To-Do List Lưu Trữ LocalStorage</t>
         </is>
       </c>
-      <c r="E46" s="16" t="inlineStr">
+      <c r="E47" s="16" t="inlineStr">
         <is>
           <t>Session 24 - Thực hành Xây dựng Ứng dụng To-Do List Lưu Trữ LocalStorage</t>
         </is>
       </c>
-      <c r="F46" s="16" t="inlineStr">
+      <c r="F47" s="16" t="inlineStr">
         <is>
           <t>Thực hành Xây dựng Ứng dụng To-Do List Lưu Trữ LocalStorage</t>
         </is>
       </c>
-      <c r="G46" s="16" t="inlineStr">
+      <c r="G47" s="16" t="inlineStr">
         <is>
           <t>Hoàn thành các mục tiêu học tập và năng lực thực hành của Thực hành Xây dựng Ứng dụng To-Do List Lưu Trữ LocalStorage.</t>
         </is>
       </c>
-      <c r="H46" s="16" t="inlineStr">
+      <c r="H47" s="16" t="inlineStr">
         <is>
           <t>CẤM: Các chủ đề nâng cao chưa học ở các buổi tiếp theo.</t>
         </is>
       </c>
-      <c r="I46" s="16" t="inlineStr">
+      <c r="I47" s="16" t="inlineStr">
         <is>
           <t>ĐÃ HỌC: Các kiến thức tiền đề đã tích lũy từ các buổi trước.</t>
         </is>
       </c>
-      <c r="J46" s="16" t="inlineStr">
-        <is>
-          <t>JavaScript Vanilla (ES6+), HTML5/CSS3, DOM API, Fetch API, Async/Await, Cursor AI IDE</t>
-        </is>
-      </c>
-    </row>
-    <row r="47" ht="24" customHeight="1">
-      <c r="A47" s="10" t="inlineStr">
+      <c r="J47" s="16" t="inlineStr">
+        <is>
+          <t>JavaScript Vanilla (ES6+), HTML5/CSS3, DOM API, Fetch API, Async/Await, Cursor AI IDE</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="24" customHeight="1">
+      <c r="A48" s="10" t="inlineStr">
         <is>
           <t>Session 25</t>
         </is>
       </c>
-      <c r="B47" s="10" t="inlineStr">
+      <c r="B48" s="10" t="inlineStr">
         <is>
           <t>Lý thuyết</t>
         </is>
       </c>
-      <c r="C47" s="10" t="inlineStr">
+      <c r="C48" s="10" t="inlineStr">
         <is>
           <t>THEORY</t>
         </is>
       </c>
-      <c r="D47" s="11" t="inlineStr">
+      <c r="D48" s="11" t="inlineStr">
         <is>
           <t>Session 25 - Dự án Web Capstone: Thiết kế Kiến trúc Frontend và Tích hợp AI Debugging</t>
         </is>
       </c>
-      <c r="E47" s="5" t="inlineStr">
+      <c r="E48" s="5" t="inlineStr">
         <is>
           <t>Lesson 01: Kiến trúc Mô-đun Frontend và Quy trình Pair-Programming AI</t>
         </is>
       </c>
-      <c r="F47" s="5" t="inlineStr">
+      <c r="F48" s="5" t="inlineStr">
         <is>
           <t>Phân rã dự án Web thành các mô-đun JS; Sử dụng Cursor AI Debug lỗi DOM và API.</t>
         </is>
       </c>
-      <c r="G47" s="5" t="inlineStr">
+      <c r="G48" s="5" t="inlineStr">
         <is>
           <t>Trình bày và thực hành thành công Kiến trúc Mô-đun Frontend và Quy trình Pair-Programming AI.</t>
         </is>
       </c>
-      <c r="H47" s="5" t="inlineStr">
-        <is>
-          <t>CẤM: Các khái niệm nâng cao chưa học ở các bài tiếp theo.</t>
-        </is>
-      </c>
-      <c r="I47" s="5" t="inlineStr">
-        <is>
-          <t>ĐÃ HỌC: Các kiến thức JS đã học ở các bài trước.</t>
-        </is>
-      </c>
-      <c r="J47" s="5" t="inlineStr">
-        <is>
-          <t>JavaScript Vanilla (ES6+), HTML5/CSS3, DOM API, Fetch API, Async/Await, Cursor AI IDE</t>
-        </is>
-      </c>
-    </row>
-    <row r="48" ht="24" customHeight="1">
-      <c r="A48" s="13" t="n"/>
-      <c r="B48" s="13" t="n"/>
-      <c r="C48" s="13" t="n"/>
-      <c r="D48" s="13" t="n"/>
-      <c r="E48" s="5" t="inlineStr">
+      <c r="H48" s="5" t="inlineStr">
+        <is>
+          <t>CẤM: Các khái niệm nâng cao chưa học ở các bài tiếp theo.</t>
+        </is>
+      </c>
+      <c r="I48" s="5" t="inlineStr">
+        <is>
+          <t>ĐÃ HỌC: Các kiến thức JS đã học ở các bài trước.</t>
+        </is>
+      </c>
+      <c r="J48" s="5" t="inlineStr">
+        <is>
+          <t>JavaScript Vanilla (ES6+), HTML5/CSS3, DOM API, Fetch API, Async/Await, Cursor AI IDE</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="24" customHeight="1">
+      <c r="A49" s="13" t="n"/>
+      <c r="B49" s="13" t="n"/>
+      <c r="C49" s="13" t="n"/>
+      <c r="D49" s="13" t="n"/>
+      <c r="E49" s="5" t="inlineStr">
         <is>
           <t>Lesson 02: Chuẩn hóa Giao diện Web Responsive và Tối ưu UI/UX</t>
         </is>
       </c>
-      <c r="F48" s="5" t="inlineStr">
+      <c r="F49" s="5" t="inlineStr">
         <is>
           <t>Kiểm thử hiển thị màn hình đa thiết bị và tối ưu trải nghiệm người dùng.</t>
         </is>
       </c>
-      <c r="G48" s="5" t="inlineStr">
+      <c r="G49" s="5" t="inlineStr">
         <is>
           <t>Trình bày và thực hành thành công Chuẩn hóa Giao diện Web Responsive và Tối ưu UI/UX.</t>
         </is>
       </c>
-      <c r="H48" s="5" t="inlineStr">
-        <is>
-          <t>CẤM: Các khái niệm nâng cao chưa học ở các bài tiếp theo.</t>
-        </is>
-      </c>
-      <c r="I48" s="5" t="inlineStr">
-        <is>
-          <t>ĐÃ HỌC: Các kiến thức JS đã học ở các bài trước.</t>
-        </is>
-      </c>
-      <c r="J48" s="5" t="inlineStr">
-        <is>
-          <t>JavaScript Vanilla (ES6+), HTML5/CSS3, DOM API, Fetch API, Async/Await, Cursor AI IDE</t>
-        </is>
-      </c>
-    </row>
-    <row r="49" ht="24" customHeight="1">
-      <c r="A49" s="23" t="inlineStr">
-        <is>
-          <t>Session 26</t>
-        </is>
-      </c>
-      <c r="B49" s="23" t="inlineStr">
-        <is>
-          <t>Project</t>
-        </is>
-      </c>
-      <c r="C49" s="23" t="inlineStr">
-        <is>
-          <t>PROJECT</t>
-        </is>
-      </c>
-      <c r="D49" s="24" t="inlineStr">
-        <is>
-          <t>Session 26 - Dự án Capstone Web (Buổi 1): Phân tích SRS và Khởi tạo Giao diện HTML/CSS</t>
-        </is>
-      </c>
-      <c r="E49" s="25" t="inlineStr">
-        <is>
-          <t>Session 26 - Dự án Capstone Web (Buổi 1): Phân tích SRS và Khởi tạo Giao diện HTML/CSS</t>
-        </is>
-      </c>
-      <c r="F49" s="25" t="inlineStr">
-        <is>
-          <t>Dự án Capstone Web (Buổi 1): Phân tích SRS và Khởi tạo Giao diện HTML/CSS</t>
-        </is>
-      </c>
-      <c r="G49" s="25" t="inlineStr">
-        <is>
-          <t>Hoàn thành các mục tiêu học tập và năng lực thực hành của Dự án Capstone Web (Buổi 1): Phân tích SRS và Khởi tạo Giao diện HTML/CSS.</t>
-        </is>
-      </c>
-      <c r="H49" s="25" t="inlineStr">
-        <is>
-          <t>CẤM: Các chủ đề nâng cao chưa học ở các buổi tiếp theo.</t>
-        </is>
-      </c>
-      <c r="I49" s="25" t="inlineStr">
-        <is>
-          <t>ĐÃ HỌC: Các kiến thức tiền đề đã tích lũy từ các buổi trước.</t>
-        </is>
-      </c>
-      <c r="J49" s="25" t="inlineStr">
+      <c r="H49" s="5" t="inlineStr">
+        <is>
+          <t>CẤM: Các khái niệm nâng cao chưa học ở các bài tiếp theo.</t>
+        </is>
+      </c>
+      <c r="I49" s="5" t="inlineStr">
+        <is>
+          <t>ĐÃ HỌC: Các kiến thức JS đã học ở các bài trước.</t>
+        </is>
+      </c>
+      <c r="J49" s="5" t="inlineStr">
         <is>
           <t>JavaScript Vanilla (ES6+), HTML5/CSS3, DOM API, Fetch API, Async/Await, Cursor AI IDE</t>
         </is>
@@ -2769,7 +2753,7 @@
     <row r="50" ht="24" customHeight="1">
       <c r="A50" s="23" t="inlineStr">
         <is>
-          <t>Session 27</t>
+          <t>Session 26</t>
         </is>
       </c>
       <c r="B50" s="23" t="inlineStr">
@@ -2784,22 +2768,22 @@
       </c>
       <c r="D50" s="24" t="inlineStr">
         <is>
-          <t>Session 27 - Dự án Capstone Web (Buổi 2): Lập trình Logic Tương tác DOM và Event Handlers</t>
+          <t>Session 26 - Dự án Capstone Web (Buổi 1): Phân tích SRS và Khởi tạo Giao diện HTML/CSS</t>
         </is>
       </c>
       <c r="E50" s="25" t="inlineStr">
         <is>
-          <t>Session 27 - Dự án Capstone Web (Buổi 2): Lập trình Logic Tương tác DOM và Event Handlers</t>
+          <t>Session 26 - Dự án Capstone Web (Buổi 1): Phân tích SRS và Khởi tạo Giao diện HTML/CSS</t>
         </is>
       </c>
       <c r="F50" s="25" t="inlineStr">
         <is>
-          <t>Dự án Capstone Web (Buổi 2): Lập trình Logic Tương tác DOM và Event Handlers</t>
+          <t>Dự án Capstone Web (Buổi 1): Phân tích SRS và Khởi tạo Giao diện HTML/CSS</t>
         </is>
       </c>
       <c r="G50" s="25" t="inlineStr">
         <is>
-          <t>Hoàn thành các mục tiêu học tập và năng lực thực hành của Dự án Capstone Web (Buổi 2): Lập trình Logic Tương tác DOM và Event Handlers.</t>
+          <t>Hoàn thành các mục tiêu học tập và năng lực thực hành của Dự án Capstone Web (Buổi 1): Phân tích SRS và Khởi tạo Giao diện HTML/CSS.</t>
         </is>
       </c>
       <c r="H50" s="25" t="inlineStr">
@@ -2821,7 +2805,7 @@
     <row r="51" ht="24" customHeight="1">
       <c r="A51" s="23" t="inlineStr">
         <is>
-          <t>Session 28</t>
+          <t>Session 27</t>
         </is>
       </c>
       <c r="B51" s="23" t="inlineStr">
@@ -2836,22 +2820,22 @@
       </c>
       <c r="D51" s="24" t="inlineStr">
         <is>
-          <t>Session 28 - Dự án Capstone Web (Buổi 3): Xử lý Dữ liệu Mảng, Object và Tích hợp LocalStorage</t>
+          <t>Session 27 - Dự án Capstone Web (Buổi 2): Lập trình Logic Tương tác DOM và Event Handlers</t>
         </is>
       </c>
       <c r="E51" s="25" t="inlineStr">
         <is>
-          <t>Session 28 - Dự án Capstone Web (Buổi 3): Xử lý Dữ liệu Mảng, Object và Tích hợp LocalStorage</t>
+          <t>Session 27 - Dự án Capstone Web (Buổi 2): Lập trình Logic Tương tác DOM và Event Handlers</t>
         </is>
       </c>
       <c r="F51" s="25" t="inlineStr">
         <is>
-          <t>Dự án Capstone Web (Buổi 3): Xử lý Dữ liệu Mảng, Object và Tích hợp LocalStorage</t>
+          <t>Dự án Capstone Web (Buổi 2): Lập trình Logic Tương tác DOM và Event Handlers</t>
         </is>
       </c>
       <c r="G51" s="25" t="inlineStr">
         <is>
-          <t>Hoàn thành các mục tiêu học tập và năng lực thực hành của Dự án Capstone Web (Buổi 3): Xử lý Dữ liệu Mảng, Object và Tích hợp LocalStorage.</t>
+          <t>Hoàn thành các mục tiêu học tập và năng lực thực hành của Dự án Capstone Web (Buổi 2): Lập trình Logic Tương tác DOM và Event Handlers.</t>
         </is>
       </c>
       <c r="H51" s="25" t="inlineStr">
@@ -2873,102 +2857,154 @@
     <row r="52" ht="24" customHeight="1">
       <c r="A52" s="23" t="inlineStr">
         <is>
+          <t>Session 28</t>
+        </is>
+      </c>
+      <c r="B52" s="23" t="inlineStr">
+        <is>
+          <t>Project</t>
+        </is>
+      </c>
+      <c r="C52" s="23" t="inlineStr">
+        <is>
+          <t>PROJECT</t>
+        </is>
+      </c>
+      <c r="D52" s="24" t="inlineStr">
+        <is>
+          <t>Session 28 - Dự án Capstone Web (Buổi 3): Xử lý Dữ liệu Mảng, Object và Tích hợp LocalStorage</t>
+        </is>
+      </c>
+      <c r="E52" s="25" t="inlineStr">
+        <is>
+          <t>Session 28 - Dự án Capstone Web (Buổi 3): Xử lý Dữ liệu Mảng, Object và Tích hợp LocalStorage</t>
+        </is>
+      </c>
+      <c r="F52" s="25" t="inlineStr">
+        <is>
+          <t>Dự án Capstone Web (Buổi 3): Xử lý Dữ liệu Mảng, Object và Tích hợp LocalStorage</t>
+        </is>
+      </c>
+      <c r="G52" s="25" t="inlineStr">
+        <is>
+          <t>Hoàn thành các mục tiêu học tập và năng lực thực hành của Dự án Capstone Web (Buổi 3): Xử lý Dữ liệu Mảng, Object và Tích hợp LocalStorage.</t>
+        </is>
+      </c>
+      <c r="H52" s="25" t="inlineStr">
+        <is>
+          <t>CẤM: Các chủ đề nâng cao chưa học ở các buổi tiếp theo.</t>
+        </is>
+      </c>
+      <c r="I52" s="25" t="inlineStr">
+        <is>
+          <t>ĐÃ HỌC: Các kiến thức tiền đề đã tích lũy từ các buổi trước.</t>
+        </is>
+      </c>
+      <c r="J52" s="25" t="inlineStr">
+        <is>
+          <t>JavaScript Vanilla (ES6+), HTML5/CSS3, DOM API, Fetch API, Async/Await, Cursor AI IDE</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="24" customHeight="1">
+      <c r="A53" s="23" t="inlineStr">
+        <is>
           <t>Session 29</t>
         </is>
       </c>
-      <c r="B52" s="23" t="inlineStr">
+      <c r="B53" s="23" t="inlineStr">
         <is>
           <t>Project</t>
         </is>
       </c>
-      <c r="C52" s="23" t="inlineStr">
+      <c r="C53" s="23" t="inlineStr">
         <is>
           <t>PROJECT</t>
         </is>
       </c>
-      <c r="D52" s="24" t="inlineStr">
+      <c r="D53" s="24" t="inlineStr">
         <is>
           <t>Session 29 - Dự án Capstone Web (Buổi 4): Gọi RESTful API Bên Ngoài và Hoàn thiện Tối ưu UI/UX</t>
         </is>
       </c>
-      <c r="E52" s="25" t="inlineStr">
+      <c r="E53" s="25" t="inlineStr">
         <is>
           <t>Session 29 - Dự án Capstone Web (Buổi 4): Gọi RESTful API Bên Ngoài và Hoàn thiện Tối ưu UI/UX</t>
         </is>
       </c>
-      <c r="F52" s="25" t="inlineStr">
+      <c r="F53" s="25" t="inlineStr">
         <is>
           <t>Dự án Capstone Web (Buổi 4): Gọi RESTful API Bên Ngoài và Hoàn thiện Tối ưu UI/UX</t>
         </is>
       </c>
-      <c r="G52" s="25" t="inlineStr">
+      <c r="G53" s="25" t="inlineStr">
         <is>
           <t>Hoàn thành các mục tiêu học tập và năng lực thực hành của Dự án Capstone Web (Buổi 4): Gọi RESTful API Bên Ngoài và Hoàn thiện Tối ưu UI/UX.</t>
         </is>
       </c>
-      <c r="H52" s="25" t="inlineStr">
+      <c r="H53" s="25" t="inlineStr">
         <is>
           <t>CẤM: Các chủ đề nâng cao chưa học ở các buổi tiếp theo.</t>
         </is>
       </c>
-      <c r="I52" s="25" t="inlineStr">
+      <c r="I53" s="25" t="inlineStr">
         <is>
           <t>ĐÃ HỌC: Các kiến thức tiền đề đã tích lũy từ các buổi trước.</t>
         </is>
       </c>
-      <c r="J52" s="25" t="inlineStr">
-        <is>
-          <t>JavaScript Vanilla (ES6+), HTML5/CSS3, DOM API, Fetch API, Async/Await, Cursor AI IDE</t>
-        </is>
-      </c>
-    </row>
-    <row r="53" ht="24" customHeight="1">
-      <c r="A53" s="20" t="inlineStr">
+      <c r="J53" s="25" t="inlineStr">
+        <is>
+          <t>JavaScript Vanilla (ES6+), HTML5/CSS3, DOM API, Fetch API, Async/Await, Cursor AI IDE</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="24" customHeight="1">
+      <c r="A54" s="20" t="inlineStr">
         <is>
           <t>Session 30</t>
         </is>
       </c>
-      <c r="B53" s="20" t="inlineStr">
+      <c r="B54" s="20" t="inlineStr">
         <is>
           <t>Thi cuối môn</t>
         </is>
       </c>
-      <c r="C53" s="20" t="inlineStr">
+      <c r="C54" s="20" t="inlineStr">
         <is>
           <t>FINAL</t>
         </is>
       </c>
-      <c r="D53" s="21" t="inlineStr">
+      <c r="D54" s="21" t="inlineStr">
         <is>
           <t>Session 30 - Bảo vệ Dự án Web Capstone và Đánh giá Năng lực Lập trình Web JS Tổng hợp</t>
         </is>
       </c>
-      <c r="E53" s="22" t="inlineStr">
+      <c r="E54" s="22" t="inlineStr">
         <is>
           <t>Session 30 - Bảo vệ Dự án Web Capstone và Đánh giá Năng lực Lập trình Web JS Tổng hợp</t>
         </is>
       </c>
-      <c r="F53" s="22" t="inlineStr">
+      <c r="F54" s="22" t="inlineStr">
         <is>
           <t>Bảo vệ Dự án Web Capstone và Đánh giá Năng lực Lập trình Web JS Tổng hợp</t>
         </is>
       </c>
-      <c r="G53" s="22" t="inlineStr">
+      <c r="G54" s="22" t="inlineStr">
         <is>
           <t>Hoàn thành các mục tiêu học tập và năng lực thực hành của Bảo vệ Dự án Web Capstone và Đánh giá Năng lực Lập trình Web JS Tổng hợp.</t>
         </is>
       </c>
-      <c r="H53" s="22" t="inlineStr">
+      <c r="H54" s="22" t="inlineStr">
         <is>
           <t>CẤM: Các chủ đề nâng cao chưa học ở các buổi tiếp theo.</t>
         </is>
       </c>
-      <c r="I53" s="22" t="inlineStr">
+      <c r="I54" s="22" t="inlineStr">
         <is>
           <t>ĐÃ HỌC: Các kiến thức tiền đề đã tích lũy từ các buổi trước.</t>
         </is>
       </c>
-      <c r="J53" s="22" t="inlineStr">
+      <c r="J54" s="22" t="inlineStr">
         <is>
           <t>JavaScript Vanilla (ES6+), HTML5/CSS3, DOM API, Fetch API, Async/Await, Cursor AI IDE</t>
         </is>
@@ -2976,60 +3012,60 @@
     </row>
   </sheetData>
   <mergeCells count="55">
+    <mergeCell ref="B27:B28"/>
+    <mergeCell ref="A48:A49"/>
     <mergeCell ref="A12:A14"/>
-    <mergeCell ref="B47:B48"/>
+    <mergeCell ref="D27:D28"/>
     <mergeCell ref="C12:C14"/>
+    <mergeCell ref="C42:C43"/>
     <mergeCell ref="D12:D14"/>
+    <mergeCell ref="C20:C21"/>
+    <mergeCell ref="C33:C34"/>
+    <mergeCell ref="B30:B32"/>
+    <mergeCell ref="A45:A46"/>
     <mergeCell ref="B1:J1"/>
-    <mergeCell ref="A29:A31"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="A41:A42"/>
-    <mergeCell ref="C16:C17"/>
-    <mergeCell ref="A22:A24"/>
-    <mergeCell ref="C26:C27"/>
-    <mergeCell ref="B38:B39"/>
-    <mergeCell ref="C44:C45"/>
-    <mergeCell ref="C35:C36"/>
-    <mergeCell ref="D32:D33"/>
+    <mergeCell ref="A36:A37"/>
+    <mergeCell ref="A23:A25"/>
+    <mergeCell ref="C45:C46"/>
+    <mergeCell ref="C23:C25"/>
+    <mergeCell ref="B42:B43"/>
+    <mergeCell ref="D36:D37"/>
+    <mergeCell ref="D45:D46"/>
+    <mergeCell ref="D23:D25"/>
+    <mergeCell ref="A27:A28"/>
+    <mergeCell ref="D30:D32"/>
+    <mergeCell ref="B39:B40"/>
+    <mergeCell ref="B48:B49"/>
     <mergeCell ref="A7:A10"/>
-    <mergeCell ref="C47:C48"/>
-    <mergeCell ref="A26:A27"/>
-    <mergeCell ref="C41:C42"/>
-    <mergeCell ref="D29:D31"/>
-    <mergeCell ref="D41:D42"/>
-    <mergeCell ref="D47:D48"/>
-    <mergeCell ref="D16:D17"/>
+    <mergeCell ref="D48:D49"/>
     <mergeCell ref="D7:D10"/>
-    <mergeCell ref="B19:B20"/>
-    <mergeCell ref="B22:B24"/>
-    <mergeCell ref="B44:B45"/>
-    <mergeCell ref="D22:D24"/>
-    <mergeCell ref="A32:A33"/>
+    <mergeCell ref="B16:B18"/>
+    <mergeCell ref="C36:C37"/>
+    <mergeCell ref="A30:A32"/>
+    <mergeCell ref="D33:D34"/>
+    <mergeCell ref="C30:C32"/>
+    <mergeCell ref="B36:B37"/>
     <mergeCell ref="B12:B14"/>
-    <mergeCell ref="A47:A48"/>
-    <mergeCell ref="C29:C31"/>
+    <mergeCell ref="A42:A43"/>
+    <mergeCell ref="A33:A34"/>
+    <mergeCell ref="C27:C28"/>
+    <mergeCell ref="B33:B34"/>
+    <mergeCell ref="A20:A21"/>
     <mergeCell ref="C7:C10"/>
-    <mergeCell ref="C32:C33"/>
-    <mergeCell ref="A19:A20"/>
-    <mergeCell ref="A44:A45"/>
-    <mergeCell ref="C19:C20"/>
-    <mergeCell ref="A35:A36"/>
-    <mergeCell ref="D19:D20"/>
-    <mergeCell ref="D44:D45"/>
+    <mergeCell ref="B20:B21"/>
+    <mergeCell ref="C39:C40"/>
+    <mergeCell ref="D42:D43"/>
+    <mergeCell ref="D20:D21"/>
+    <mergeCell ref="C48:C49"/>
+    <mergeCell ref="B45:B46"/>
+    <mergeCell ref="D39:D40"/>
+    <mergeCell ref="B23:B25"/>
     <mergeCell ref="B3:J3"/>
-    <mergeCell ref="B32:B33"/>
-    <mergeCell ref="A38:A39"/>
-    <mergeCell ref="C38:C39"/>
-    <mergeCell ref="D26:D27"/>
-    <mergeCell ref="D38:D39"/>
-    <mergeCell ref="D35:D36"/>
-    <mergeCell ref="B29:B31"/>
-    <mergeCell ref="B41:B42"/>
-    <mergeCell ref="B16:B17"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="C16:C18"/>
+    <mergeCell ref="A39:A40"/>
     <mergeCell ref="B7:B10"/>
-    <mergeCell ref="B26:B27"/>
-    <mergeCell ref="C22:C24"/>
-    <mergeCell ref="B35:B36"/>
+    <mergeCell ref="D16:D18"/>
     <mergeCell ref="B2:J2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
